--- a/Driver_Experience.xlsx
+++ b/Driver_Experience.xlsx
@@ -8,13 +8,25 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{F9469F4B-9EEA-424B-BBA1-E68A2D684C22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CA5004-E96A-4BD5-9514-2725E80081B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28590" yWindow="-10980" windowWidth="16410" windowHeight="11295" activeTab="1" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" firstSheet="6" activeTab="12" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
-    <sheet name="2002" sheetId="2" r:id="rId2"/>
+    <sheet name="1991" sheetId="3" r:id="rId2"/>
+    <sheet name="1992" sheetId="4" r:id="rId3"/>
+    <sheet name="1993" sheetId="5" r:id="rId4"/>
+    <sheet name="1994" sheetId="6" r:id="rId5"/>
+    <sheet name="1995" sheetId="7" r:id="rId6"/>
+    <sheet name="1996" sheetId="8" r:id="rId7"/>
+    <sheet name="1997" sheetId="9" r:id="rId8"/>
+    <sheet name="1998" sheetId="10" r:id="rId9"/>
+    <sheet name="1999" sheetId="11" r:id="rId10"/>
+    <sheet name="2000" sheetId="12" r:id="rId11"/>
+    <sheet name="2001" sheetId="13" r:id="rId12"/>
+    <sheet name="2002" sheetId="2" r:id="rId13"/>
+    <sheet name="2003" sheetId="14" r:id="rId14"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +46,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="51">
   <si>
     <t>Driver</t>
   </si>
@@ -160,6 +172,33 @@
   </si>
   <si>
     <t>Japan</t>
+  </si>
+  <si>
+    <t>Mexico</t>
+  </si>
+  <si>
+    <t>Portugal</t>
+  </si>
+  <si>
+    <t>South Africa</t>
+  </si>
+  <si>
+    <t>Fernando Alonso</t>
+  </si>
+  <si>
+    <t>Ralph Firman</t>
+  </si>
+  <si>
+    <t>Antônio Pizzonia</t>
+  </si>
+  <si>
+    <t>Jos Verstappen</t>
+  </si>
+  <si>
+    <t>Justin Wilson</t>
+  </si>
+  <si>
+    <t>Cristiano da Matta</t>
   </si>
 </sst>
 </file>
@@ -302,7 +341,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -480,6 +519,12 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.39997558519241921"/>
         <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -643,8 +688,10 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1020,13 +1067,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AR23"/>
+  <dimension ref="A1:AL29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1141,144 +1189,418 @@
       <c r="AL1">
         <v>1991</v>
       </c>
-      <c r="AM1">
-        <v>1990</v>
-      </c>
-      <c r="AN1">
-        <v>1989</v>
-      </c>
-      <c r="AO1">
-        <v>1988</v>
-      </c>
-      <c r="AP1">
-        <v>1987</v>
-      </c>
-      <c r="AQ1">
-        <v>1986</v>
-      </c>
-      <c r="AR1">
-        <v>1985</v>
-      </c>
-    </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="AA2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="AJ2">
+        <v>16</v>
+      </c>
+      <c r="AK2">
+        <v>16</v>
+      </c>
+      <c r="AL2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AJ3">
+        <v>14</v>
+      </c>
+      <c r="AK3" s="1"/>
+      <c r="AL3" s="1"/>
+    </row>
+    <row r="4" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AC4" s="1"/>
+      <c r="AD4" s="1"/>
+      <c r="AE4" s="1"/>
+      <c r="AF4" s="1"/>
+      <c r="AG4" s="1"/>
+      <c r="AH4" s="1"/>
+      <c r="AI4" s="1"/>
+      <c r="AJ4" s="1"/>
+      <c r="AK4" s="1"/>
+      <c r="AL4" s="1"/>
+    </row>
+    <row r="5" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AJ5" s="1"/>
+      <c r="AK5" s="1"/>
+      <c r="AL5" s="1"/>
+    </row>
+    <row r="6" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AC6" s="1"/>
+      <c r="AD6" s="1"/>
+      <c r="AE6" s="1"/>
+      <c r="AF6" s="1"/>
+      <c r="AG6" s="1"/>
+      <c r="AH6" s="1"/>
+      <c r="AI6" s="1"/>
+      <c r="AJ6" s="1"/>
+      <c r="AK6" s="1"/>
+      <c r="AL6" s="1"/>
+    </row>
+    <row r="7" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AG7" s="1"/>
+      <c r="AH7" s="1"/>
+      <c r="AI7" s="1"/>
+      <c r="AJ7" s="1"/>
+      <c r="AK7" s="1"/>
+      <c r="AL7" s="1"/>
+    </row>
+    <row r="8" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AB8" s="1"/>
+      <c r="AC8" s="1"/>
+      <c r="AD8" s="1"/>
+      <c r="AE8" s="1"/>
+      <c r="AF8" s="1"/>
+      <c r="AG8" s="1"/>
+      <c r="AH8" s="1"/>
+      <c r="AI8" s="1"/>
+      <c r="AJ8" s="1"/>
+      <c r="AK8" s="1"/>
+      <c r="AL8" s="1"/>
+    </row>
+    <row r="9" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AD9" s="1"/>
+      <c r="AE9" s="1"/>
+      <c r="AF9" s="1"/>
+      <c r="AG9" s="1"/>
+      <c r="AH9" s="1"/>
+      <c r="AI9" s="1"/>
+      <c r="AJ9" s="1"/>
+      <c r="AK9" s="1"/>
+      <c r="AL9" s="1"/>
+    </row>
+    <row r="10" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AH10" s="1"/>
+      <c r="AI10" s="1"/>
+      <c r="AJ10" s="1"/>
+      <c r="AK10" s="1"/>
+      <c r="AL10" s="1"/>
+    </row>
+    <row r="11" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AJ11" s="1"/>
+      <c r="AK11" s="1"/>
+      <c r="AL11" s="1"/>
+    </row>
+    <row r="12" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AD12" s="1"/>
+      <c r="AE12" s="1"/>
+      <c r="AF12" s="1"/>
+      <c r="AG12" s="1"/>
+      <c r="AH12" s="1"/>
+      <c r="AI12" s="1"/>
+      <c r="AJ12" s="1"/>
+      <c r="AK12" s="1"/>
+      <c r="AL12" s="1"/>
+    </row>
+    <row r="13" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AG13" s="1"/>
+      <c r="AH13" s="1"/>
+      <c r="AI13" s="1"/>
+      <c r="AJ13" s="1"/>
+      <c r="AK13" s="1"/>
+      <c r="AL13" s="1"/>
+    </row>
+    <row r="14" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="15" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AB14" s="1"/>
+      <c r="AC14" s="1"/>
+      <c r="AD14" s="1"/>
+      <c r="AE14" s="1"/>
+      <c r="AF14" s="1"/>
+      <c r="AG14" s="1"/>
+      <c r="AH14" s="1"/>
+      <c r="AI14" s="1"/>
+      <c r="AJ14" s="1"/>
+      <c r="AK14" s="1"/>
+      <c r="AL14" s="1"/>
+    </row>
+    <row r="15" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AH15" s="1"/>
+      <c r="AI15" s="1"/>
+      <c r="AJ15" s="1"/>
+      <c r="AK15" s="1"/>
+      <c r="AL15" s="1"/>
+    </row>
+    <row r="16" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="AE16" s="1"/>
+      <c r="AF16" s="1"/>
+      <c r="AG16" s="1"/>
+      <c r="AH16" s="1"/>
+      <c r="AI16" s="1"/>
+      <c r="AJ16" s="1"/>
+      <c r="AK16" s="1"/>
+      <c r="AL16" s="1"/>
+    </row>
+    <row r="17" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="AJ17">
+        <v>2</v>
+      </c>
+      <c r="AK17" s="1"/>
+      <c r="AL17" s="1"/>
+    </row>
+    <row r="18" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="AB18" s="1"/>
+      <c r="AC18" s="1"/>
+      <c r="AD18" s="1"/>
+      <c r="AE18" s="1"/>
+      <c r="AF18" s="1"/>
+      <c r="AG18" s="1"/>
+      <c r="AH18" s="1"/>
+      <c r="AI18" s="1"/>
+      <c r="AJ18" s="1"/>
+      <c r="AK18" s="1"/>
+      <c r="AL18" s="1"/>
+    </row>
+    <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="AC19" s="1"/>
+      <c r="AD19" s="1"/>
+      <c r="AE19" s="1"/>
+      <c r="AF19" s="1"/>
+      <c r="AG19" s="1"/>
+      <c r="AH19" s="1"/>
+      <c r="AI19" s="1"/>
+      <c r="AJ19" s="1"/>
+      <c r="AK19" s="1"/>
+      <c r="AL19" s="1"/>
+    </row>
+    <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="AC20" s="1"/>
+      <c r="AD20" s="1"/>
+      <c r="AE20" s="1"/>
+      <c r="AF20" s="1"/>
+      <c r="AG20" s="1"/>
+      <c r="AH20" s="1"/>
+      <c r="AI20" s="1"/>
+      <c r="AJ20" s="1"/>
+      <c r="AK20" s="1"/>
+      <c r="AL20" s="1"/>
+    </row>
+    <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="AJ21" s="1"/>
+      <c r="AK21" s="1"/>
+      <c r="AL21" s="1"/>
+    </row>
+    <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="AJ22" s="1"/>
+      <c r="AK22" s="1"/>
+      <c r="AL22" s="1"/>
+    </row>
+    <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
+      <c r="AB23" s="1"/>
+      <c r="AC23" s="1"/>
+      <c r="AD23" s="1"/>
+      <c r="AE23" s="1"/>
+      <c r="AF23" s="1"/>
+      <c r="AG23" s="1"/>
+      <c r="AH23" s="1"/>
+      <c r="AI23" s="1"/>
+      <c r="AJ23" s="1"/>
+      <c r="AK23" s="1"/>
+      <c r="AL23" s="1"/>
+    </row>
+    <row r="24" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC24" s="1"/>
+      <c r="AD24" s="1"/>
+      <c r="AE24" s="1"/>
+      <c r="AF24" s="1"/>
+      <c r="AG24" s="1"/>
+      <c r="AH24" s="1"/>
+      <c r="AI24" s="1"/>
+      <c r="AJ24" s="1"/>
+      <c r="AK24" s="1"/>
+      <c r="AL24" s="1"/>
+    </row>
+    <row r="25" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA25" s="1"/>
+      <c r="AB25" s="1"/>
+      <c r="AC25" s="1"/>
+      <c r="AD25" s="1"/>
+      <c r="AE25" s="1"/>
+      <c r="AF25" s="1"/>
+      <c r="AG25" s="1"/>
+      <c r="AH25" s="1"/>
+      <c r="AI25" s="1"/>
+      <c r="AJ25" s="1"/>
+      <c r="AK25" s="1"/>
+      <c r="AL25" s="1"/>
+    </row>
+    <row r="26" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>47</v>
+      </c>
+      <c r="AA26" s="1"/>
+      <c r="AB26" s="1"/>
+      <c r="AC26" s="1"/>
+      <c r="AD26" s="1"/>
+      <c r="AE26" s="1"/>
+      <c r="AF26" s="1"/>
+      <c r="AG26" s="1"/>
+      <c r="AH26" s="1"/>
+      <c r="AI26" s="1"/>
+      <c r="AJ26" s="1"/>
+      <c r="AK26" s="1"/>
+      <c r="AL26" s="1"/>
+    </row>
+    <row r="27" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>48</v>
+      </c>
+      <c r="AJ27" s="1"/>
+      <c r="AK27" s="1"/>
+      <c r="AL27" s="1"/>
+    </row>
+    <row r="28" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>49</v>
+      </c>
+      <c r="AA28" s="1"/>
+      <c r="AB28" s="1"/>
+      <c r="AC28" s="1"/>
+      <c r="AD28" s="1"/>
+      <c r="AE28" s="1"/>
+      <c r="AF28" s="1"/>
+      <c r="AG28" s="1"/>
+      <c r="AH28" s="1"/>
+      <c r="AI28" s="1"/>
+      <c r="AJ28" s="1"/>
+      <c r="AK28" s="1"/>
+      <c r="AL28" s="1"/>
+    </row>
+    <row r="29" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA29" s="1"/>
+      <c r="AB29" s="1"/>
+      <c r="AC29" s="1"/>
+      <c r="AD29" s="1"/>
+      <c r="AE29" s="1"/>
+      <c r="AF29" s="1"/>
+      <c r="AG29" s="1"/>
+      <c r="AH29" s="1"/>
+      <c r="AI29" s="1"/>
+      <c r="AJ29" s="1"/>
+      <c r="AK29" s="1"/>
+      <c r="AL29" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A672F957-1D62-4580-B7C6-2DFEBD8C86A9}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFC06B72-571E-40C4-AD69-3294909EA05A}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5463DBD5-1047-4E7D-B3B5-A719C2F7680D}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7053FD00-70E4-44ED-874D-48591AC61FE1}">
   <dimension ref="A1:S23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1290,6 +1612,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
       <c r="B1" t="s">
         <v>24</v>
       </c>
@@ -1351,9 +1676,15 @@
       </c>
       <c r="B2">
         <f>SUM(C2:C2:S2)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
         <v>1</v>
       </c>
     </row>
@@ -1363,9 +1694,15 @@
       </c>
       <c r="B3">
         <f>SUM(C3:C3:S3)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
         <v>1</v>
       </c>
     </row>
@@ -1375,9 +1712,15 @@
       </c>
       <c r="B4">
         <f>SUM(C4:C4:S4)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
         <v>1</v>
       </c>
     </row>
@@ -1387,9 +1730,15 @@
       </c>
       <c r="B5">
         <f>SUM(C5:C5:S5)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
         <v>1</v>
       </c>
     </row>
@@ -1399,9 +1748,15 @@
       </c>
       <c r="B6">
         <f>SUM(C6:C6:S6)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
     </row>
@@ -1411,9 +1766,15 @@
       </c>
       <c r="B7">
         <f>SUM(C7:C7:S7)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
         <v>1</v>
       </c>
     </row>
@@ -1423,9 +1784,15 @@
       </c>
       <c r="B8">
         <f>SUM(C8:C8:S8)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
     </row>
@@ -1435,9 +1802,15 @@
       </c>
       <c r="B9">
         <f>SUM(C9:C9:S9)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
         <v>1</v>
       </c>
     </row>
@@ -1447,9 +1820,15 @@
       </c>
       <c r="B10">
         <f>SUM(C10:C10:S10)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10">
+        <v>1</v>
+      </c>
+      <c r="E10">
         <v>1</v>
       </c>
     </row>
@@ -1459,9 +1838,15 @@
       </c>
       <c r="B11">
         <f>SUM(C11:C11:S11)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="E11">
         <v>1</v>
       </c>
     </row>
@@ -1471,9 +1856,15 @@
       </c>
       <c r="B12">
         <f>SUM(C12:C12:S12)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="D12">
+        <v>1</v>
+      </c>
+      <c r="E12">
         <v>1</v>
       </c>
     </row>
@@ -1483,9 +1874,15 @@
       </c>
       <c r="B13">
         <f>SUM(C13:C13:S13)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C13">
+        <v>1</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="E13">
         <v>1</v>
       </c>
     </row>
@@ -1495,9 +1892,15 @@
       </c>
       <c r="B14">
         <f>SUM(C14:C14:S14)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C14">
+        <v>1</v>
+      </c>
+      <c r="D14">
+        <v>1</v>
+      </c>
+      <c r="E14">
         <v>1</v>
       </c>
     </row>
@@ -1507,9 +1910,15 @@
       </c>
       <c r="B15">
         <f>SUM(C15:C15:S15)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C15">
+        <v>1</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15">
         <v>1</v>
       </c>
     </row>
@@ -1519,97 +1928,874 @@
       </c>
       <c r="B16">
         <f>SUM(C16:C16:S16)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C16">
         <v>1</v>
       </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D16">
+        <v>1</v>
+      </c>
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17">
         <f>SUM(C17:C17:S17)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C17">
         <v>1</v>
       </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="B18">
         <f>SUM(C18:C18:S18)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D18">
+        <v>1</v>
+      </c>
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>19</v>
       </c>
       <c r="B19">
         <f>SUM(C19:C19:S19)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C19">
         <v>1</v>
       </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D19">
+        <v>1</v>
+      </c>
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>20</v>
       </c>
       <c r="B20">
         <f>SUM(C20:C20:S20)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D20">
+        <v>1</v>
+      </c>
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>21</v>
       </c>
       <c r="B21">
         <f>SUM(C21:C21:S21)</f>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>22</v>
       </c>
       <c r="B22">
         <f>SUM(C22:C22:S22)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="D22">
+        <v>1</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>23</v>
       </c>
       <c r="B23">
         <f>SUM(C23:C23:S23)</f>
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="C23">
+        <v>1</v>
+      </c>
+      <c r="D23">
+        <v>1</v>
+      </c>
+      <c r="E23">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
+  <dimension ref="A1:B22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="4.85546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>50</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EC39A2-025A-41B3-9C60-22F202BB8868}">
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>0</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <v>0</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+      <c r="I2">
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BBA742C1-0B95-4CA1-8FA2-14D0BE967B15}">
+  <dimension ref="A1:R2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="9" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>42</v>
+      </c>
+      <c r="E1" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D2BC23-0382-4C73-BD55-9C5BF90A5872}">
+  <dimension ref="A1:R4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" customWidth="1"/>
+    <col min="3" max="3" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E1" t="s">
+        <v>33</v>
+      </c>
+      <c r="F1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
+        <v>31</v>
+      </c>
+      <c r="I1" t="s">
+        <v>32</v>
+      </c>
+      <c r="J1" t="s">
+        <v>35</v>
+      </c>
+      <c r="K1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M1" t="s">
+        <v>37</v>
+      </c>
+      <c r="N1" t="s">
+        <v>38</v>
+      </c>
+      <c r="O1" t="s">
+        <v>39</v>
+      </c>
+      <c r="P1" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>16</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B4" si="0">SUM(C3:R3)</f>
+        <v>14</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>0</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>0</v>
+      </c>
+      <c r="K4">
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <v>0</v>
+      </c>
+      <c r="M4">
+        <v>0</v>
+      </c>
+      <c r="N4">
+        <v>0</v>
+      </c>
+      <c r="O4">
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD508AD-7632-48CF-B894-9F6914C08CD8}">
+  <dimension ref="A1:B9"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1668A00-6C37-4B7D-B869-26E922968418}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6443FC8D-E56E-407E-83EA-E01E6A3300AE}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Driver_Experience.xlsx
+++ b/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56CA5004-E96A-4BD5-9514-2725E80081B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F803CDEC-0708-4AB6-9F8F-4DF322B09974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" firstSheet="6" activeTab="12" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" activeTab="4" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -19,14 +19,37 @@
     <sheet name="1993" sheetId="5" r:id="rId4"/>
     <sheet name="1994" sheetId="6" r:id="rId5"/>
     <sheet name="1995" sheetId="7" r:id="rId6"/>
-    <sheet name="1996" sheetId="8" r:id="rId7"/>
-    <sheet name="1997" sheetId="9" r:id="rId8"/>
+    <sheet name="1997" sheetId="9" r:id="rId7"/>
+    <sheet name="1996" sheetId="8" r:id="rId8"/>
     <sheet name="1998" sheetId="10" r:id="rId9"/>
     <sheet name="1999" sheetId="11" r:id="rId10"/>
     <sheet name="2000" sheetId="12" r:id="rId11"/>
     <sheet name="2001" sheetId="13" r:id="rId12"/>
     <sheet name="2002" sheetId="2" r:id="rId13"/>
     <sheet name="2003" sheetId="14" r:id="rId14"/>
+    <sheet name="2004" sheetId="15" r:id="rId15"/>
+    <sheet name="2005" sheetId="16" r:id="rId16"/>
+    <sheet name="2006" sheetId="17" r:id="rId17"/>
+    <sheet name="2007" sheetId="18" r:id="rId18"/>
+    <sheet name="2008" sheetId="19" r:id="rId19"/>
+    <sheet name="2009" sheetId="20" r:id="rId20"/>
+    <sheet name="2010" sheetId="21" r:id="rId21"/>
+    <sheet name="2011" sheetId="22" r:id="rId22"/>
+    <sheet name="2012" sheetId="23" r:id="rId23"/>
+    <sheet name="2013" sheetId="24" r:id="rId24"/>
+    <sheet name="2014" sheetId="25" r:id="rId25"/>
+    <sheet name="2015" sheetId="26" r:id="rId26"/>
+    <sheet name="2016" sheetId="27" r:id="rId27"/>
+    <sheet name="2017" sheetId="28" r:id="rId28"/>
+    <sheet name="2018" sheetId="29" r:id="rId29"/>
+    <sheet name="2019" sheetId="30" r:id="rId30"/>
+    <sheet name="2020" sheetId="31" r:id="rId31"/>
+    <sheet name="2021" sheetId="32" r:id="rId32"/>
+    <sheet name="2022" sheetId="33" r:id="rId33"/>
+    <sheet name="2023" sheetId="34" r:id="rId34"/>
+    <sheet name="2024" sheetId="35" r:id="rId35"/>
+    <sheet name="2025" sheetId="36" r:id="rId36"/>
+    <sheet name="2026" sheetId="37" r:id="rId37"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -46,7 +69,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="870" uniqueCount="153">
   <si>
     <t>Driver</t>
   </si>
@@ -199,6 +222,312 @@
   </si>
   <si>
     <t>Cristiano da Matta</t>
+  </si>
+  <si>
+    <t>Pacific</t>
+  </si>
+  <si>
+    <t>Argentina</t>
+  </si>
+  <si>
+    <t>Anthony Davidson</t>
+  </si>
+  <si>
+    <t>Marc Gene</t>
+  </si>
+  <si>
+    <t>Fernando Alonso</t>
+  </si>
+  <si>
+    <t>Heinz-Harald Frentzen</t>
+  </si>
+  <si>
+    <t>Cristiano da Matta</t>
+  </si>
+  <si>
+    <t>Ralph Firman</t>
+  </si>
+  <si>
+    <t>Justin Wilson</t>
+  </si>
+  <si>
+    <t>Antonio Pizzonia</t>
+  </si>
+  <si>
+    <t>Nicolas Kiesa</t>
+  </si>
+  <si>
+    <t>Zsolt Baumgartner</t>
+  </si>
+  <si>
+    <t>Christian Klien</t>
+  </si>
+  <si>
+    <t>Timo Glock</t>
+  </si>
+  <si>
+    <t>Ricardo Zonta</t>
+  </si>
+  <si>
+    <t>Giorgio Pantano</t>
+  </si>
+  <si>
+    <t>Gianmaria Bruni</t>
+  </si>
+  <si>
+    <t>Tiago Monteiro</t>
+  </si>
+  <si>
+    <t>Alexander Wurz</t>
+  </si>
+  <si>
+    <t>Narain Karthikeyan</t>
+  </si>
+  <si>
+    <t>Christijan Albers</t>
+  </si>
+  <si>
+    <t>Patrick Friesacher</t>
+  </si>
+  <si>
+    <t>Vitantonio Liuzzi</t>
+  </si>
+  <si>
+    <t>Robert Doornbos</t>
+  </si>
+  <si>
+    <t>Robert Kubica</t>
+  </si>
+  <si>
+    <t>Nico Rosberg</t>
+  </si>
+  <si>
+    <t>Scott Speed</t>
+  </si>
+  <si>
+    <t>Yuji Ide</t>
+  </si>
+  <si>
+    <t>Sakon Yamamoto</t>
+  </si>
+  <si>
+    <t>Franck Montagny</t>
+  </si>
+  <si>
+    <t>Lewis Hamilton</t>
+  </si>
+  <si>
+    <t>Heikki Kovalainen</t>
+  </si>
+  <si>
+    <t>Sebastian Vettel</t>
+  </si>
+  <si>
+    <t>Adrian Sutil</t>
+  </si>
+  <si>
+    <t>Kazuki Nakajima</t>
+  </si>
+  <si>
+    <t>Anthony Davidson</t>
+  </si>
+  <si>
+    <t>Nelson Piquet</t>
+  </si>
+  <si>
+    <t>Sebastien Bourdais</t>
+  </si>
+  <si>
+    <t>Sebastien Buemi</t>
+  </si>
+  <si>
+    <t>Kamui Kobayashi</t>
+  </si>
+  <si>
+    <t>Romain Grosjean</t>
+  </si>
+  <si>
+    <t>Jaime Alguersuari</t>
+  </si>
+  <si>
+    <t>Luca Badoer</t>
+  </si>
+  <si>
+    <t>Vitaly Petrov</t>
+  </si>
+  <si>
+    <t>Nico Hulkenberg</t>
+  </si>
+  <si>
+    <t>Karun Chandhok</t>
+  </si>
+  <si>
+    <t>Bruno Senna</t>
+  </si>
+  <si>
+    <t>Lucas di Grassi</t>
+  </si>
+  <si>
+    <t>Paul di Resta</t>
+  </si>
+  <si>
+    <t>Sergio Perez</t>
+  </si>
+  <si>
+    <t>Pastor Maldonado</t>
+  </si>
+  <si>
+    <t>Jerome d'Ambrosio</t>
+  </si>
+  <si>
+    <t>Daniel Ricciardo</t>
+  </si>
+  <si>
+    <t>Jean-Eric Vergne</t>
+  </si>
+  <si>
+    <t>Charles Pic</t>
+  </si>
+  <si>
+    <t>Esteban Gutierrez</t>
+  </si>
+  <si>
+    <t>Valtteri Bottas</t>
+  </si>
+  <si>
+    <t>Jules Bianchi</t>
+  </si>
+  <si>
+    <t>Giedo van der Garde</t>
+  </si>
+  <si>
+    <t>Max Chilton</t>
+  </si>
+  <si>
+    <t>Kevin Magnussen</t>
+  </si>
+  <si>
+    <t>Daniil Kvyat</t>
+  </si>
+  <si>
+    <t>Marcus Ericsson</t>
+  </si>
+  <si>
+    <t>Will Stevens</t>
+  </si>
+  <si>
+    <t>Max Verstappen</t>
+  </si>
+  <si>
+    <t>Felipe Nasr</t>
+  </si>
+  <si>
+    <t>Carlos Sainz</t>
+  </si>
+  <si>
+    <t>Roberto Merhi</t>
+  </si>
+  <si>
+    <t>Alexander Rossi</t>
+  </si>
+  <si>
+    <t>Jolyon Palmer</t>
+  </si>
+  <si>
+    <t>Pascal Wehrlein</t>
+  </si>
+  <si>
+    <t>Stoffel Vandoorne</t>
+  </si>
+  <si>
+    <t>Esteban Ocon</t>
+  </si>
+  <si>
+    <t>Rio Haryanto</t>
+  </si>
+  <si>
+    <t>Lance Stroll</t>
+  </si>
+  <si>
+    <t>Pierre Gasly</t>
+  </si>
+  <si>
+    <t>Antonio Giovinazzi</t>
+  </si>
+  <si>
+    <t>Brendon Hartley</t>
+  </si>
+  <si>
+    <t>Charles Leclerc</t>
+  </si>
+  <si>
+    <t>Sergey Sirotkin</t>
+  </si>
+  <si>
+    <t>Alexander Albon</t>
+  </si>
+  <si>
+    <t>Lando Norris</t>
+  </si>
+  <si>
+    <t>George Russell</t>
+  </si>
+  <si>
+    <t>Nicholas Latifi</t>
+  </si>
+  <si>
+    <t>Jack Aitken</t>
+  </si>
+  <si>
+    <t>Pietro Fittipaldi</t>
+  </si>
+  <si>
+    <t>Yuki Tsunoda</t>
+  </si>
+  <si>
+    <t>Mick Schumacher</t>
+  </si>
+  <si>
+    <t>Nikita Mazepin</t>
+  </si>
+  <si>
+    <t>Zhou Guanyu</t>
+  </si>
+  <si>
+    <t>Nyck De Vries</t>
+  </si>
+  <si>
+    <t>Oscar Piastri</t>
+  </si>
+  <si>
+    <t>Liam Lawson</t>
+  </si>
+  <si>
+    <t>Logan Sargeant</t>
+  </si>
+  <si>
+    <t>Oliver Bearman</t>
+  </si>
+  <si>
+    <t>Franco Colapinto</t>
+  </si>
+  <si>
+    <t>Jack Doohan</t>
+  </si>
+  <si>
+    <t>Kimi Antonelli</t>
+  </si>
+  <si>
+    <t>Isack Hadjar</t>
+  </si>
+  <si>
+    <t>Gabriel Bortoleto</t>
+  </si>
+  <si>
+    <t>Arvid Lindblad</t>
+  </si>
+  <si>
+    <t>.</t>
   </si>
 </sst>
 </file>
@@ -523,7 +852,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1"/>
+        <fgColor theme="0" tint="-0.249977111117893"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -748,6 +1077,212 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="AutoShape 19">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0A3E2722-7405-4FAD-9FFE-86DD60A773DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>144</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>145</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="3" name="AutoShape 21">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{58D26C26-931C-4DA0-A2E4-9DD2AA59A5EB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37907" name="AutoShape 19">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70C39A74-EDC8-0411-5885-812B0B5C9F85}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37909" name="AutoShape 21">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{119FC7EB-B2FF-3FE9-DA70-A559D5ECCC2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="0" y="3619500"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1067,7 +1602,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CCEEE69D-1A9D-4213-BBC7-B7EBD153B749}">
-  <dimension ref="A1:AL29"/>
+  <dimension ref="A1:AL126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -1208,6 +1743,16 @@
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
       <c r="AJ2">
         <v>16</v>
       </c>
@@ -1222,6 +1767,30 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2"/>
+      <c r="P3" s="2"/>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2"/>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2"/>
+      <c r="U3" s="2"/>
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
       <c r="AJ3">
         <v>14</v>
       </c>
@@ -1232,6 +1801,30 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
+      <c r="P4" s="2"/>
+      <c r="Q4" s="2"/>
+      <c r="R4" s="2"/>
+      <c r="S4" s="2"/>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2"/>
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
@@ -1247,6 +1840,30 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2"/>
+      <c r="P5" s="2"/>
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2"/>
+      <c r="S5" s="2"/>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
@@ -1255,6 +1872,30 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2"/>
+      <c r="P6" s="2"/>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2"/>
+      <c r="S6" s="2"/>
+      <c r="T6" s="2"/>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
@@ -1270,6 +1911,30 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2"/>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" s="2"/>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2"/>
+      <c r="S7" s="2"/>
+      <c r="T7" s="2"/>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -1281,6 +1946,30 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2"/>
+      <c r="P8" s="2"/>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2"/>
+      <c r="S8" s="2"/>
+      <c r="T8" s="2"/>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
@@ -1297,6 +1986,30 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2"/>
+      <c r="P9" s="2"/>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2"/>
+      <c r="S9" s="2"/>
+      <c r="T9" s="2"/>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
@@ -1311,6 +2024,32 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2"/>
+      <c r="P10" s="2"/>
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2"/>
+      <c r="S10" s="2"/>
+      <c r="T10" s="2"/>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2" t="s">
+        <v>152</v>
+      </c>
       <c r="AH10" s="1"/>
       <c r="AI10" s="1"/>
       <c r="AJ10" s="1"/>
@@ -1321,6 +2060,30 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2"/>
+      <c r="P11" s="2"/>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2"/>
+      <c r="S11" s="2"/>
+      <c r="T11" s="2"/>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
@@ -1329,6 +2092,30 @@
       <c r="A12" t="s">
         <v>12</v>
       </c>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2"/>
+      <c r="P12" s="2"/>
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2"/>
+      <c r="S12" s="2"/>
+      <c r="T12" s="2"/>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
@@ -1343,6 +2130,30 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+      <c r="F13" s="2"/>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2"/>
+      <c r="P13" s="2"/>
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2"/>
+      <c r="S13" s="2"/>
+      <c r="T13" s="2"/>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
@@ -1354,6 +2165,30 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
+      <c r="F14" s="2"/>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2"/>
+      <c r="P14" s="2"/>
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2"/>
+      <c r="S14" s="2"/>
+      <c r="T14" s="2"/>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
@@ -1370,6 +2205,30 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2"/>
+      <c r="P15" s="2"/>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2"/>
+      <c r="S15" s="2"/>
+      <c r="T15" s="2"/>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -1380,6 +2239,30 @@
       <c r="A16" t="s">
         <v>16</v>
       </c>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2"/>
+      <c r="P16" s="2"/>
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2"/>
+      <c r="S16" s="2"/>
+      <c r="T16" s="2"/>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
@@ -1393,6 +2276,30 @@
       <c r="A17" t="s">
         <v>17</v>
       </c>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2"/>
+      <c r="P17" s="2"/>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2"/>
+      <c r="S17" s="2"/>
+      <c r="T17" s="2"/>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
       <c r="AJ17">
         <v>2</v>
       </c>
@@ -1403,6 +2310,30 @@
       <c r="A18" t="s">
         <v>18</v>
       </c>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
@@ -1417,8 +2348,33 @@
     </row>
     <row r="19" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+      <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
       <c r="AE19" s="1"/>
@@ -1432,8 +2388,32 @@
     </row>
     <row r="20" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
-      </c>
+        <v>19</v>
+      </c>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
@@ -1447,40 +2427,136 @@
     </row>
     <row r="21" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+      <c r="AC21" s="1"/>
+      <c r="AD21" s="1"/>
+      <c r="AE21" s="1"/>
+      <c r="AF21" s="1"/>
+      <c r="AG21" s="1"/>
+      <c r="AH21" s="1"/>
+      <c r="AI21" s="1"/>
       <c r="AJ21" s="1"/>
       <c r="AK21" s="1"/>
       <c r="AL21" s="1"/>
     </row>
     <row r="22" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
     </row>
     <row r="23" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
-      </c>
-      <c r="AB23" s="1"/>
-      <c r="AC23" s="1"/>
-      <c r="AD23" s="1"/>
-      <c r="AE23" s="1"/>
-      <c r="AF23" s="1"/>
-      <c r="AG23" s="1"/>
-      <c r="AH23" s="1"/>
-      <c r="AI23" s="1"/>
+        <v>22</v>
+      </c>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
     </row>
     <row r="24" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>45</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+      <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
       <c r="AE24" s="1"/>
@@ -1494,10 +2570,8 @@
     </row>
     <row r="25" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA25" s="1"/>
-      <c r="AB25" s="1"/>
+        <v>45</v>
+      </c>
       <c r="AC25" s="1"/>
       <c r="AD25" s="1"/>
       <c r="AE25" s="1"/>
@@ -1511,8 +2585,32 @@
     </row>
     <row r="26" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>47</v>
-      </c>
+        <v>46</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
@@ -1528,32 +2626,32 @@
     </row>
     <row r="27" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>48</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="AA27" s="1"/>
+      <c r="AB27" s="1"/>
+      <c r="AC27" s="1"/>
+      <c r="AD27" s="1"/>
+      <c r="AE27" s="1"/>
+      <c r="AF27" s="1"/>
+      <c r="AG27" s="1"/>
+      <c r="AH27" s="1"/>
+      <c r="AI27" s="1"/>
       <c r="AJ27" s="1"/>
       <c r="AK27" s="1"/>
       <c r="AL27" s="1"/>
     </row>
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>49</v>
-      </c>
-      <c r="AA28" s="1"/>
-      <c r="AB28" s="1"/>
-      <c r="AC28" s="1"/>
-      <c r="AD28" s="1"/>
-      <c r="AE28" s="1"/>
-      <c r="AF28" s="1"/>
-      <c r="AG28" s="1"/>
-      <c r="AH28" s="1"/>
-      <c r="AI28" s="1"/>
+        <v>48</v>
+      </c>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
       <c r="AL28" s="1"/>
     </row>
     <row r="29" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AA29" s="1"/>
       <c r="AB29" s="1"/>
@@ -1568,8 +2666,2524 @@
       <c r="AK29" s="1"/>
       <c r="AL29" s="1"/>
     </row>
+    <row r="30" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>50</v>
+      </c>
+      <c r="AA30" s="1"/>
+      <c r="AB30" s="1"/>
+      <c r="AC30" s="1"/>
+      <c r="AD30" s="1"/>
+      <c r="AE30" s="1"/>
+      <c r="AF30" s="1"/>
+      <c r="AG30" s="1"/>
+      <c r="AH30" s="1"/>
+      <c r="AI30" s="1"/>
+      <c r="AJ30" s="1"/>
+      <c r="AK30" s="1"/>
+      <c r="AL30" s="1"/>
+    </row>
+    <row r="31" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC31" s="1"/>
+      <c r="AD31" s="1"/>
+      <c r="AE31" s="1"/>
+      <c r="AF31" s="1"/>
+      <c r="AG31" s="1"/>
+      <c r="AH31" s="1"/>
+      <c r="AI31" s="1"/>
+      <c r="AJ31" s="1"/>
+      <c r="AK31" s="1"/>
+      <c r="AL31" s="1"/>
+    </row>
+    <row r="32" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA32" s="1"/>
+      <c r="AB32" s="1"/>
+      <c r="AC32" s="1"/>
+      <c r="AD32" s="1"/>
+      <c r="AE32" s="1"/>
+      <c r="AF32" s="1"/>
+      <c r="AG32" s="1"/>
+      <c r="AH32" s="1"/>
+      <c r="AI32" s="1"/>
+      <c r="AJ32" s="1"/>
+      <c r="AK32" s="1"/>
+      <c r="AL32" s="1"/>
+    </row>
+    <row r="33" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>54</v>
+      </c>
+      <c r="AE33" s="1"/>
+      <c r="AF33" s="1"/>
+      <c r="AG33" s="1"/>
+      <c r="AH33" s="1"/>
+      <c r="AI33" s="1"/>
+      <c r="AJ33" s="1"/>
+      <c r="AK33" s="1"/>
+      <c r="AL33" s="1"/>
+    </row>
+    <row r="34" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>58</v>
+      </c>
+      <c r="AA34" s="1"/>
+      <c r="AB34" s="1"/>
+      <c r="AC34" s="1"/>
+      <c r="AD34" s="1"/>
+      <c r="AE34" s="1"/>
+      <c r="AF34" s="1"/>
+      <c r="AG34" s="1"/>
+      <c r="AH34" s="1"/>
+      <c r="AI34" s="1"/>
+      <c r="AJ34" s="1"/>
+      <c r="AK34" s="1"/>
+      <c r="AL34" s="1"/>
+    </row>
+    <row r="35" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>59</v>
+      </c>
+      <c r="AA35" s="1"/>
+      <c r="AB35" s="1"/>
+      <c r="AC35" s="1"/>
+      <c r="AD35" s="1"/>
+      <c r="AE35" s="1"/>
+      <c r="AF35" s="1"/>
+      <c r="AG35" s="1"/>
+      <c r="AH35" s="1"/>
+      <c r="AI35" s="1"/>
+      <c r="AJ35" s="1"/>
+      <c r="AK35" s="1"/>
+      <c r="AL35" s="1"/>
+    </row>
+    <row r="36" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>60</v>
+      </c>
+      <c r="AA36" s="1"/>
+      <c r="AB36" s="1"/>
+      <c r="AC36" s="1"/>
+      <c r="AD36" s="1"/>
+      <c r="AE36" s="1"/>
+      <c r="AF36" s="1"/>
+      <c r="AG36" s="1"/>
+      <c r="AH36" s="1"/>
+      <c r="AI36" s="1"/>
+      <c r="AJ36" s="1"/>
+      <c r="AK36" s="1"/>
+      <c r="AL36" s="1"/>
+    </row>
+    <row r="37" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>61</v>
+      </c>
+      <c r="AA37" s="1"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="1"/>
+      <c r="AD37" s="1"/>
+      <c r="AE37" s="1"/>
+      <c r="AF37" s="1"/>
+      <c r="AG37" s="1"/>
+      <c r="AH37" s="1"/>
+      <c r="AI37" s="1"/>
+      <c r="AJ37" s="1"/>
+      <c r="AK37" s="1"/>
+      <c r="AL37" s="1"/>
+    </row>
+    <row r="38" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>62</v>
+      </c>
+      <c r="AA38" s="1"/>
+      <c r="AB38" s="1"/>
+      <c r="AC38" s="1"/>
+      <c r="AD38" s="1"/>
+      <c r="AE38" s="1"/>
+      <c r="AF38" s="1"/>
+      <c r="AG38" s="1"/>
+      <c r="AH38" s="1"/>
+      <c r="AI38" s="1"/>
+      <c r="AJ38" s="1"/>
+      <c r="AK38" s="1"/>
+      <c r="AL38" s="1"/>
+    </row>
+    <row r="39" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>63</v>
+      </c>
+      <c r="Z39" s="1"/>
+      <c r="AA39" s="1"/>
+      <c r="AB39" s="1"/>
+      <c r="AC39" s="1"/>
+      <c r="AD39" s="1"/>
+      <c r="AE39" s="1"/>
+      <c r="AF39" s="1"/>
+      <c r="AG39" s="1"/>
+      <c r="AH39" s="1"/>
+      <c r="AI39" s="1"/>
+      <c r="AJ39" s="1"/>
+      <c r="AK39" s="1"/>
+      <c r="AL39" s="1"/>
+    </row>
+    <row r="40" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>64</v>
+      </c>
+      <c r="Z40" s="1"/>
+      <c r="AA40" s="1"/>
+      <c r="AB40" s="1"/>
+      <c r="AC40" s="1"/>
+      <c r="AD40" s="1"/>
+      <c r="AE40" s="1"/>
+      <c r="AF40" s="1"/>
+      <c r="AG40" s="1"/>
+      <c r="AH40" s="1"/>
+      <c r="AI40" s="1"/>
+      <c r="AJ40" s="1"/>
+      <c r="AK40" s="1"/>
+      <c r="AL40" s="1"/>
+    </row>
+    <row r="41" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>65</v>
+      </c>
+      <c r="AE41" s="1"/>
+      <c r="AF41" s="1"/>
+      <c r="AG41" s="1"/>
+      <c r="AH41" s="1"/>
+      <c r="AI41" s="1"/>
+      <c r="AJ41" s="1"/>
+      <c r="AK41" s="1"/>
+      <c r="AL41" s="1"/>
+    </row>
+    <row r="42" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>66</v>
+      </c>
+      <c r="Z42" s="1"/>
+      <c r="AA42" s="1"/>
+      <c r="AB42" s="1"/>
+      <c r="AC42" s="1"/>
+      <c r="AD42" s="1"/>
+      <c r="AE42" s="1"/>
+      <c r="AF42" s="1"/>
+      <c r="AG42" s="1"/>
+      <c r="AH42" s="1"/>
+      <c r="AI42" s="1"/>
+      <c r="AJ42" s="1"/>
+      <c r="AK42" s="1"/>
+      <c r="AL42" s="1"/>
+    </row>
+    <row r="43" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>67</v>
+      </c>
+      <c r="Z43" s="1"/>
+      <c r="AA43" s="1"/>
+      <c r="AB43" s="1"/>
+      <c r="AC43" s="1"/>
+      <c r="AD43" s="1"/>
+      <c r="AE43" s="1"/>
+      <c r="AF43" s="1"/>
+      <c r="AG43" s="1"/>
+      <c r="AH43" s="1"/>
+      <c r="AI43" s="1"/>
+      <c r="AJ43" s="1"/>
+      <c r="AK43" s="1"/>
+      <c r="AL43" s="1"/>
+    </row>
+    <row r="44" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>68</v>
+      </c>
+      <c r="Y44" s="1"/>
+      <c r="Z44" s="1"/>
+      <c r="AA44" s="1"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="1"/>
+      <c r="AD44" s="1"/>
+      <c r="AE44" s="1"/>
+      <c r="AF44" s="1"/>
+      <c r="AG44" s="1"/>
+      <c r="AH44" s="1"/>
+      <c r="AI44" s="1"/>
+      <c r="AJ44" s="1"/>
+      <c r="AK44" s="1"/>
+      <c r="AL44" s="1"/>
+    </row>
+    <row r="45" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>69</v>
+      </c>
+      <c r="AG45" s="1"/>
+      <c r="AH45" s="1"/>
+      <c r="AI45" s="1"/>
+      <c r="AJ45" s="1"/>
+      <c r="AK45" s="1"/>
+      <c r="AL45" s="1"/>
+    </row>
+    <row r="46" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y46" s="1"/>
+      <c r="Z46" s="1"/>
+      <c r="AA46" s="1"/>
+      <c r="AB46" s="1"/>
+      <c r="AC46" s="1"/>
+      <c r="AD46" s="1"/>
+      <c r="AE46" s="1"/>
+      <c r="AF46" s="1"/>
+      <c r="AG46" s="1"/>
+      <c r="AH46" s="1"/>
+      <c r="AI46" s="1"/>
+      <c r="AJ46" s="1"/>
+      <c r="AK46" s="1"/>
+      <c r="AL46" s="1"/>
+    </row>
+    <row r="47" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>71</v>
+      </c>
+      <c r="Y47" s="1"/>
+      <c r="Z47" s="1"/>
+      <c r="AA47" s="1"/>
+      <c r="AB47" s="1"/>
+      <c r="AC47" s="1"/>
+      <c r="AD47" s="1"/>
+      <c r="AE47" s="1"/>
+      <c r="AF47" s="1"/>
+      <c r="AG47" s="1"/>
+      <c r="AH47" s="1"/>
+      <c r="AI47" s="1"/>
+      <c r="AJ47" s="1"/>
+      <c r="AK47" s="1"/>
+      <c r="AL47" s="1"/>
+    </row>
+    <row r="48" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y48" s="1"/>
+      <c r="Z48" s="1"/>
+      <c r="AA48" s="1"/>
+      <c r="AB48" s="1"/>
+      <c r="AC48" s="1"/>
+      <c r="AD48" s="1"/>
+      <c r="AE48" s="1"/>
+      <c r="AF48" s="1"/>
+      <c r="AG48" s="1"/>
+      <c r="AH48" s="1"/>
+      <c r="AI48" s="1"/>
+      <c r="AJ48" s="1"/>
+      <c r="AK48" s="1"/>
+      <c r="AL48" s="1"/>
+    </row>
+    <row r="49" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y49" s="1"/>
+      <c r="Z49" s="1"/>
+      <c r="AA49" s="1"/>
+      <c r="AB49" s="1"/>
+      <c r="AC49" s="1"/>
+      <c r="AD49" s="1"/>
+      <c r="AE49" s="1"/>
+      <c r="AF49" s="1"/>
+      <c r="AG49" s="1"/>
+      <c r="AH49" s="1"/>
+      <c r="AI49" s="1"/>
+      <c r="AJ49" s="1"/>
+      <c r="AK49" s="1"/>
+      <c r="AL49" s="1"/>
+    </row>
+    <row r="50" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>74</v>
+      </c>
+      <c r="Y50" s="1"/>
+      <c r="Z50" s="1"/>
+      <c r="AA50" s="1"/>
+      <c r="AB50" s="1"/>
+      <c r="AC50" s="1"/>
+      <c r="AD50" s="1"/>
+      <c r="AE50" s="1"/>
+      <c r="AF50" s="1"/>
+      <c r="AG50" s="1"/>
+      <c r="AH50" s="1"/>
+      <c r="AI50" s="1"/>
+      <c r="AJ50" s="1"/>
+      <c r="AK50" s="1"/>
+      <c r="AL50" s="1"/>
+    </row>
+    <row r="51" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>75</v>
+      </c>
+      <c r="X51" s="1"/>
+      <c r="Y51" s="1"/>
+      <c r="Z51" s="1"/>
+      <c r="AA51" s="1"/>
+      <c r="AB51" s="1"/>
+      <c r="AC51" s="1"/>
+      <c r="AD51" s="1"/>
+      <c r="AE51" s="1"/>
+      <c r="AF51" s="1"/>
+      <c r="AG51" s="1"/>
+      <c r="AH51" s="1"/>
+      <c r="AI51" s="1"/>
+      <c r="AJ51" s="1"/>
+      <c r="AK51" s="1"/>
+      <c r="AL51" s="1"/>
+    </row>
+    <row r="52" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>76</v>
+      </c>
+      <c r="X52" s="1"/>
+      <c r="Y52" s="1"/>
+      <c r="Z52" s="1"/>
+      <c r="AA52" s="1"/>
+      <c r="AB52" s="1"/>
+      <c r="AC52" s="1"/>
+      <c r="AD52" s="1"/>
+      <c r="AE52" s="1"/>
+      <c r="AF52" s="1"/>
+      <c r="AG52" s="1"/>
+      <c r="AH52" s="1"/>
+      <c r="AI52" s="1"/>
+      <c r="AJ52" s="1"/>
+      <c r="AK52" s="1"/>
+      <c r="AL52" s="1"/>
+    </row>
+    <row r="53" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>77</v>
+      </c>
+      <c r="X53" s="1"/>
+      <c r="Y53" s="1"/>
+      <c r="Z53" s="1"/>
+      <c r="AA53" s="1"/>
+      <c r="AB53" s="1"/>
+      <c r="AC53" s="1"/>
+      <c r="AD53" s="1"/>
+      <c r="AE53" s="1"/>
+      <c r="AF53" s="1"/>
+      <c r="AG53" s="1"/>
+      <c r="AH53" s="1"/>
+      <c r="AI53" s="1"/>
+      <c r="AJ53" s="1"/>
+      <c r="AK53" s="1"/>
+      <c r="AL53" s="1"/>
+    </row>
+    <row r="54" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>78</v>
+      </c>
+      <c r="X54" s="1"/>
+      <c r="Y54" s="1"/>
+      <c r="Z54" s="1"/>
+      <c r="AA54" s="1"/>
+      <c r="AB54" s="1"/>
+      <c r="AC54" s="1"/>
+      <c r="AD54" s="1"/>
+      <c r="AE54" s="1"/>
+      <c r="AF54" s="1"/>
+      <c r="AG54" s="1"/>
+      <c r="AH54" s="1"/>
+      <c r="AI54" s="1"/>
+      <c r="AJ54" s="1"/>
+      <c r="AK54" s="1"/>
+      <c r="AL54" s="1"/>
+    </row>
+    <row r="55" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>79</v>
+      </c>
+      <c r="X55" s="1"/>
+      <c r="Y55" s="1"/>
+      <c r="Z55" s="1"/>
+      <c r="AA55" s="1"/>
+      <c r="AB55" s="1"/>
+      <c r="AC55" s="1"/>
+      <c r="AD55" s="1"/>
+      <c r="AE55" s="1"/>
+      <c r="AF55" s="1"/>
+      <c r="AG55" s="1"/>
+      <c r="AH55" s="1"/>
+      <c r="AI55" s="1"/>
+      <c r="AJ55" s="1"/>
+      <c r="AK55" s="1"/>
+      <c r="AL55" s="1"/>
+    </row>
+    <row r="56" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>80</v>
+      </c>
+      <c r="X56" s="1"/>
+      <c r="Y56" s="1"/>
+      <c r="Z56" s="1"/>
+      <c r="AA56" s="1"/>
+      <c r="AB56" s="1"/>
+      <c r="AC56" s="1"/>
+      <c r="AD56" s="1"/>
+      <c r="AE56" s="1"/>
+      <c r="AF56" s="1"/>
+      <c r="AG56" s="1"/>
+      <c r="AH56" s="1"/>
+      <c r="AI56" s="1"/>
+      <c r="AJ56" s="1"/>
+      <c r="AK56" s="1"/>
+      <c r="AL56" s="1"/>
+    </row>
+    <row r="57" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>81</v>
+      </c>
+      <c r="W57" s="1"/>
+      <c r="X57" s="1"/>
+      <c r="Y57" s="1"/>
+      <c r="Z57" s="1"/>
+      <c r="AA57" s="1"/>
+      <c r="AB57" s="1"/>
+      <c r="AC57" s="1"/>
+      <c r="AD57" s="1"/>
+      <c r="AE57" s="1"/>
+      <c r="AF57" s="1"/>
+      <c r="AG57" s="1"/>
+      <c r="AH57" s="1"/>
+      <c r="AI57" s="1"/>
+      <c r="AJ57" s="1"/>
+      <c r="AK57" s="1"/>
+      <c r="AL57" s="1"/>
+    </row>
+    <row r="58" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>82</v>
+      </c>
+      <c r="W58" s="1"/>
+      <c r="X58" s="1"/>
+      <c r="Y58" s="1"/>
+      <c r="Z58" s="1"/>
+      <c r="AA58" s="1"/>
+      <c r="AB58" s="1"/>
+      <c r="AC58" s="1"/>
+      <c r="AD58" s="1"/>
+      <c r="AE58" s="1"/>
+      <c r="AF58" s="1"/>
+      <c r="AG58" s="1"/>
+      <c r="AH58" s="1"/>
+      <c r="AI58" s="1"/>
+      <c r="AJ58" s="1"/>
+      <c r="AK58" s="1"/>
+      <c r="AL58" s="1"/>
+    </row>
+    <row r="59" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>83</v>
+      </c>
+      <c r="W59" s="1"/>
+      <c r="X59" s="1"/>
+      <c r="Y59" s="1"/>
+      <c r="Z59" s="1"/>
+      <c r="AA59" s="1"/>
+      <c r="AB59" s="1"/>
+      <c r="AC59" s="1"/>
+      <c r="AD59" s="1"/>
+      <c r="AE59" s="1"/>
+      <c r="AF59" s="1"/>
+      <c r="AG59" s="1"/>
+      <c r="AH59" s="1"/>
+      <c r="AI59" s="1"/>
+      <c r="AJ59" s="1"/>
+      <c r="AK59" s="1"/>
+      <c r="AL59" s="1"/>
+    </row>
+    <row r="60" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>84</v>
+      </c>
+      <c r="W60" s="1"/>
+      <c r="X60" s="1"/>
+      <c r="Y60" s="1"/>
+      <c r="Z60" s="1"/>
+      <c r="AA60" s="1"/>
+      <c r="AB60" s="1"/>
+      <c r="AC60" s="1"/>
+      <c r="AD60" s="1"/>
+      <c r="AE60" s="1"/>
+      <c r="AF60" s="1"/>
+      <c r="AG60" s="1"/>
+      <c r="AH60" s="1"/>
+      <c r="AI60" s="1"/>
+      <c r="AJ60" s="1"/>
+      <c r="AK60" s="1"/>
+      <c r="AL60" s="1"/>
+    </row>
+    <row r="61" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>85</v>
+      </c>
+      <c r="W61" s="1"/>
+      <c r="X61" s="1"/>
+      <c r="Y61" s="1"/>
+      <c r="Z61" s="1"/>
+      <c r="AA61" s="1"/>
+      <c r="AB61" s="1"/>
+      <c r="AC61" s="1"/>
+      <c r="AD61" s="1"/>
+      <c r="AE61" s="1"/>
+      <c r="AF61" s="1"/>
+      <c r="AG61" s="1"/>
+      <c r="AH61" s="1"/>
+      <c r="AI61" s="1"/>
+      <c r="AJ61" s="1"/>
+      <c r="AK61" s="1"/>
+      <c r="AL61" s="1"/>
+    </row>
+    <row r="62" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>87</v>
+      </c>
+      <c r="V62" s="1"/>
+      <c r="W62" s="1"/>
+      <c r="X62" s="1"/>
+      <c r="Y62" s="1"/>
+      <c r="Z62" s="1"/>
+      <c r="AA62" s="1"/>
+      <c r="AB62" s="1"/>
+      <c r="AC62" s="1"/>
+      <c r="AD62" s="1"/>
+      <c r="AE62" s="1"/>
+      <c r="AF62" s="1"/>
+      <c r="AG62" s="1"/>
+      <c r="AH62" s="1"/>
+      <c r="AI62" s="1"/>
+      <c r="AJ62" s="1"/>
+      <c r="AK62" s="1"/>
+      <c r="AL62" s="1"/>
+    </row>
+    <row r="63" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>88</v>
+      </c>
+      <c r="V63" s="1"/>
+      <c r="W63" s="1"/>
+      <c r="X63" s="1"/>
+      <c r="Y63" s="1"/>
+      <c r="Z63" s="1"/>
+      <c r="AA63" s="1"/>
+      <c r="AB63" s="1"/>
+      <c r="AC63" s="1"/>
+      <c r="AD63" s="1"/>
+      <c r="AE63" s="1"/>
+      <c r="AF63" s="1"/>
+      <c r="AG63" s="1"/>
+      <c r="AH63" s="1"/>
+      <c r="AI63" s="1"/>
+      <c r="AJ63" s="1"/>
+      <c r="AK63" s="1"/>
+      <c r="AL63" s="1"/>
+    </row>
+    <row r="64" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>89</v>
+      </c>
+      <c r="U64" s="1"/>
+      <c r="V64" s="1"/>
+      <c r="W64" s="1"/>
+      <c r="X64" s="1"/>
+      <c r="Y64" s="1"/>
+      <c r="Z64" s="1"/>
+      <c r="AA64" s="1"/>
+      <c r="AB64" s="1"/>
+      <c r="AC64" s="1"/>
+      <c r="AD64" s="1"/>
+      <c r="AE64" s="1"/>
+      <c r="AF64" s="1"/>
+      <c r="AG64" s="1"/>
+      <c r="AH64" s="1"/>
+      <c r="AI64" s="1"/>
+      <c r="AJ64" s="1"/>
+      <c r="AK64" s="1"/>
+      <c r="AL64" s="1"/>
+    </row>
+    <row r="65" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>90</v>
+      </c>
+      <c r="U65" s="1"/>
+      <c r="V65" s="1"/>
+      <c r="W65" s="1"/>
+      <c r="X65" s="1"/>
+      <c r="Y65" s="1"/>
+      <c r="Z65" s="1"/>
+      <c r="AA65" s="1"/>
+      <c r="AB65" s="1"/>
+      <c r="AC65" s="1"/>
+      <c r="AD65" s="1"/>
+      <c r="AE65" s="1"/>
+      <c r="AF65" s="1"/>
+      <c r="AG65" s="1"/>
+      <c r="AH65" s="1"/>
+      <c r="AI65" s="1"/>
+      <c r="AJ65" s="1"/>
+      <c r="AK65" s="1"/>
+      <c r="AL65" s="1"/>
+    </row>
+    <row r="66" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>91</v>
+      </c>
+      <c r="U66" s="1"/>
+      <c r="V66" s="1"/>
+      <c r="W66" s="1"/>
+      <c r="X66" s="1"/>
+      <c r="Y66" s="1"/>
+      <c r="Z66" s="1"/>
+      <c r="AA66" s="1"/>
+      <c r="AB66" s="1"/>
+      <c r="AC66" s="1"/>
+      <c r="AD66" s="1"/>
+      <c r="AE66" s="1"/>
+      <c r="AF66" s="1"/>
+      <c r="AG66" s="1"/>
+      <c r="AH66" s="1"/>
+      <c r="AI66" s="1"/>
+      <c r="AJ66" s="1"/>
+      <c r="AK66" s="1"/>
+      <c r="AL66" s="1"/>
+    </row>
+    <row r="67" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>92</v>
+      </c>
+      <c r="U67" s="1"/>
+      <c r="V67" s="1"/>
+      <c r="W67" s="1"/>
+      <c r="X67" s="1"/>
+      <c r="Y67" s="1"/>
+      <c r="Z67" s="1"/>
+      <c r="AA67" s="1"/>
+      <c r="AB67" s="1"/>
+      <c r="AC67" s="1"/>
+      <c r="AD67" s="1"/>
+      <c r="AE67" s="1"/>
+      <c r="AF67" s="1"/>
+      <c r="AG67" s="1"/>
+      <c r="AH67" s="1"/>
+      <c r="AI67" s="1"/>
+      <c r="AJ67" s="1"/>
+      <c r="AK67" s="1"/>
+      <c r="AL67" s="1"/>
+    </row>
+    <row r="68" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>93</v>
+      </c>
+      <c r="AH68" s="1"/>
+      <c r="AI68" s="1"/>
+      <c r="AJ68" s="1"/>
+      <c r="AK68" s="1"/>
+      <c r="AL68" s="1"/>
+    </row>
+    <row r="69" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>94</v>
+      </c>
+      <c r="T69" s="1"/>
+      <c r="U69" s="1"/>
+      <c r="V69" s="1"/>
+      <c r="W69" s="1"/>
+      <c r="X69" s="1"/>
+      <c r="Y69" s="1"/>
+      <c r="Z69" s="1"/>
+      <c r="AA69" s="1"/>
+      <c r="AB69" s="1"/>
+      <c r="AC69" s="1"/>
+      <c r="AD69" s="1"/>
+      <c r="AE69" s="1"/>
+      <c r="AF69" s="1"/>
+      <c r="AG69" s="1"/>
+      <c r="AH69" s="1"/>
+      <c r="AI69" s="1"/>
+      <c r="AJ69" s="1"/>
+      <c r="AK69" s="1"/>
+      <c r="AL69" s="1"/>
+    </row>
+    <row r="70" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>95</v>
+      </c>
+      <c r="T70" s="1"/>
+      <c r="U70" s="1"/>
+      <c r="V70" s="1"/>
+      <c r="W70" s="1"/>
+      <c r="X70" s="1"/>
+      <c r="Y70" s="1"/>
+      <c r="Z70" s="1"/>
+      <c r="AA70" s="1"/>
+      <c r="AB70" s="1"/>
+      <c r="AC70" s="1"/>
+      <c r="AD70" s="1"/>
+      <c r="AE70" s="1"/>
+      <c r="AF70" s="1"/>
+      <c r="AG70" s="1"/>
+      <c r="AH70" s="1"/>
+      <c r="AI70" s="1"/>
+      <c r="AJ70" s="1"/>
+      <c r="AK70" s="1"/>
+      <c r="AL70" s="1"/>
+    </row>
+    <row r="71" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>96</v>
+      </c>
+      <c r="T71" s="1"/>
+      <c r="U71" s="1"/>
+      <c r="V71" s="1"/>
+      <c r="W71" s="1"/>
+      <c r="X71" s="1"/>
+      <c r="Y71" s="1"/>
+      <c r="Z71" s="1"/>
+      <c r="AA71" s="1"/>
+      <c r="AB71" s="1"/>
+      <c r="AC71" s="1"/>
+      <c r="AD71" s="1"/>
+      <c r="AE71" s="1"/>
+      <c r="AF71" s="1"/>
+      <c r="AG71" s="1"/>
+      <c r="AH71" s="1"/>
+      <c r="AI71" s="1"/>
+      <c r="AJ71" s="1"/>
+      <c r="AK71" s="1"/>
+      <c r="AL71" s="1"/>
+    </row>
+    <row r="72" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>97</v>
+      </c>
+      <c r="T72" s="1"/>
+      <c r="U72" s="1"/>
+      <c r="V72" s="1"/>
+      <c r="W72" s="1"/>
+      <c r="X72" s="1"/>
+      <c r="Y72" s="1"/>
+      <c r="Z72" s="1"/>
+      <c r="AA72" s="1"/>
+      <c r="AB72" s="1"/>
+      <c r="AC72" s="1"/>
+      <c r="AD72" s="1"/>
+      <c r="AE72" s="1"/>
+      <c r="AF72" s="1"/>
+      <c r="AG72" s="1"/>
+      <c r="AH72" s="1"/>
+      <c r="AI72" s="1"/>
+      <c r="AJ72" s="1"/>
+      <c r="AK72" s="1"/>
+      <c r="AL72" s="1"/>
+    </row>
+    <row r="73" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>98</v>
+      </c>
+      <c r="T73" s="1"/>
+      <c r="U73" s="1"/>
+      <c r="V73" s="1"/>
+      <c r="W73" s="1"/>
+      <c r="X73" s="1"/>
+      <c r="Y73" s="1"/>
+      <c r="Z73" s="1"/>
+      <c r="AA73" s="1"/>
+      <c r="AB73" s="1"/>
+      <c r="AC73" s="1"/>
+      <c r="AD73" s="1"/>
+      <c r="AE73" s="1"/>
+      <c r="AF73" s="1"/>
+      <c r="AG73" s="1"/>
+      <c r="AH73" s="1"/>
+      <c r="AI73" s="1"/>
+      <c r="AJ73" s="1"/>
+      <c r="AK73" s="1"/>
+      <c r="AL73" s="1"/>
+    </row>
+    <row r="74" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>99</v>
+      </c>
+      <c r="S74" s="1"/>
+      <c r="T74" s="1"/>
+      <c r="U74" s="1"/>
+      <c r="V74" s="1"/>
+      <c r="W74" s="1"/>
+      <c r="X74" s="1"/>
+      <c r="Y74" s="1"/>
+      <c r="Z74" s="1"/>
+      <c r="AA74" s="1"/>
+      <c r="AB74" s="1"/>
+      <c r="AC74" s="1"/>
+      <c r="AD74" s="1"/>
+      <c r="AE74" s="1"/>
+      <c r="AF74" s="1"/>
+      <c r="AG74" s="1"/>
+      <c r="AH74" s="1"/>
+      <c r="AI74" s="1"/>
+      <c r="AJ74" s="1"/>
+      <c r="AK74" s="1"/>
+      <c r="AL74" s="1"/>
+    </row>
+    <row r="75" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>100</v>
+      </c>
+      <c r="S75" s="1"/>
+      <c r="T75" s="1"/>
+      <c r="U75" s="1"/>
+      <c r="V75" s="1"/>
+      <c r="W75" s="1"/>
+      <c r="X75" s="1"/>
+      <c r="Y75" s="1"/>
+      <c r="Z75" s="1"/>
+      <c r="AA75" s="1"/>
+      <c r="AB75" s="1"/>
+      <c r="AC75" s="1"/>
+      <c r="AD75" s="1"/>
+      <c r="AE75" s="1"/>
+      <c r="AF75" s="1"/>
+      <c r="AG75" s="1"/>
+      <c r="AH75" s="1"/>
+      <c r="AI75" s="1"/>
+      <c r="AJ75" s="1"/>
+      <c r="AK75" s="1"/>
+      <c r="AL75" s="1"/>
+    </row>
+    <row r="76" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>101</v>
+      </c>
+      <c r="S76" s="1"/>
+      <c r="T76" s="1"/>
+      <c r="U76" s="1"/>
+      <c r="V76" s="1"/>
+      <c r="W76" s="1"/>
+      <c r="X76" s="1"/>
+      <c r="Y76" s="1"/>
+      <c r="Z76" s="1"/>
+      <c r="AA76" s="1"/>
+      <c r="AB76" s="1"/>
+      <c r="AC76" s="1"/>
+      <c r="AD76" s="1"/>
+      <c r="AE76" s="1"/>
+      <c r="AF76" s="1"/>
+      <c r="AG76" s="1"/>
+      <c r="AH76" s="1"/>
+      <c r="AI76" s="1"/>
+      <c r="AJ76" s="1"/>
+      <c r="AK76" s="1"/>
+      <c r="AL76" s="1"/>
+    </row>
+    <row r="77" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>102</v>
+      </c>
+      <c r="S77" s="1"/>
+      <c r="T77" s="1"/>
+      <c r="U77" s="1"/>
+      <c r="V77" s="1"/>
+      <c r="W77" s="1"/>
+      <c r="X77" s="1"/>
+      <c r="Y77" s="1"/>
+      <c r="Z77" s="1"/>
+      <c r="AA77" s="1"/>
+      <c r="AB77" s="1"/>
+      <c r="AC77" s="1"/>
+      <c r="AD77" s="1"/>
+      <c r="AE77" s="1"/>
+      <c r="AF77" s="1"/>
+      <c r="AG77" s="1"/>
+      <c r="AH77" s="1"/>
+      <c r="AI77" s="1"/>
+      <c r="AJ77" s="1"/>
+      <c r="AK77" s="1"/>
+      <c r="AL77" s="1"/>
+    </row>
+    <row r="78" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>103</v>
+      </c>
+      <c r="S78" s="1"/>
+      <c r="T78" s="1"/>
+      <c r="U78" s="1"/>
+      <c r="V78" s="1"/>
+      <c r="W78" s="1"/>
+      <c r="X78" s="1"/>
+      <c r="Y78" s="1"/>
+      <c r="Z78" s="1"/>
+      <c r="AA78" s="1"/>
+      <c r="AB78" s="1"/>
+      <c r="AC78" s="1"/>
+      <c r="AD78" s="1"/>
+      <c r="AE78" s="1"/>
+      <c r="AF78" s="1"/>
+      <c r="AG78" s="1"/>
+      <c r="AH78" s="1"/>
+      <c r="AI78" s="1"/>
+      <c r="AJ78" s="1"/>
+      <c r="AK78" s="1"/>
+      <c r="AL78" s="1"/>
+    </row>
+    <row r="79" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>104</v>
+      </c>
+      <c r="R79" s="1"/>
+      <c r="S79" s="1"/>
+      <c r="T79" s="1"/>
+      <c r="U79" s="1"/>
+      <c r="V79" s="1"/>
+      <c r="W79" s="1"/>
+      <c r="X79" s="1"/>
+      <c r="Y79" s="1"/>
+      <c r="Z79" s="1"/>
+      <c r="AA79" s="1"/>
+      <c r="AB79" s="1"/>
+      <c r="AC79" s="1"/>
+      <c r="AD79" s="1"/>
+      <c r="AE79" s="1"/>
+      <c r="AF79" s="1"/>
+      <c r="AG79" s="1"/>
+      <c r="AH79" s="1"/>
+      <c r="AI79" s="1"/>
+      <c r="AJ79" s="1"/>
+      <c r="AK79" s="1"/>
+      <c r="AL79" s="1"/>
+    </row>
+    <row r="80" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>105</v>
+      </c>
+      <c r="R80" s="1"/>
+      <c r="S80" s="1"/>
+      <c r="T80" s="1"/>
+      <c r="U80" s="1"/>
+      <c r="V80" s="1"/>
+      <c r="W80" s="1"/>
+      <c r="X80" s="1"/>
+      <c r="Y80" s="1"/>
+      <c r="Z80" s="1"/>
+      <c r="AA80" s="1"/>
+      <c r="AB80" s="1"/>
+      <c r="AC80" s="1"/>
+      <c r="AD80" s="1"/>
+      <c r="AE80" s="1"/>
+      <c r="AF80" s="1"/>
+      <c r="AG80" s="1"/>
+      <c r="AH80" s="1"/>
+      <c r="AI80" s="1"/>
+      <c r="AJ80" s="1"/>
+      <c r="AK80" s="1"/>
+      <c r="AL80" s="1"/>
+    </row>
+    <row r="81" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>106</v>
+      </c>
+      <c r="Q81" s="1"/>
+      <c r="R81" s="1"/>
+      <c r="S81" s="1"/>
+      <c r="T81" s="1"/>
+      <c r="U81" s="1"/>
+      <c r="V81" s="1"/>
+      <c r="W81" s="1"/>
+      <c r="X81" s="1"/>
+      <c r="Y81" s="1"/>
+      <c r="Z81" s="1"/>
+      <c r="AA81" s="1"/>
+      <c r="AB81" s="1"/>
+      <c r="AC81" s="1"/>
+      <c r="AD81" s="1"/>
+      <c r="AE81" s="1"/>
+      <c r="AF81" s="1"/>
+      <c r="AG81" s="1"/>
+      <c r="AH81" s="1"/>
+      <c r="AI81" s="1"/>
+      <c r="AJ81" s="1"/>
+      <c r="AK81" s="1"/>
+      <c r="AL81" s="1"/>
+    </row>
+    <row r="82" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q82" s="1"/>
+      <c r="R82" s="1"/>
+      <c r="S82" s="1"/>
+      <c r="T82" s="1"/>
+      <c r="U82" s="1"/>
+      <c r="V82" s="1"/>
+      <c r="W82" s="1"/>
+      <c r="X82" s="1"/>
+      <c r="Y82" s="1"/>
+      <c r="Z82" s="1"/>
+      <c r="AA82" s="1"/>
+      <c r="AB82" s="1"/>
+      <c r="AC82" s="1"/>
+      <c r="AD82" s="1"/>
+      <c r="AE82" s="1"/>
+      <c r="AF82" s="1"/>
+      <c r="AG82" s="1"/>
+      <c r="AH82" s="1"/>
+      <c r="AI82" s="1"/>
+      <c r="AJ82" s="1"/>
+      <c r="AK82" s="1"/>
+      <c r="AL82" s="1"/>
+    </row>
+    <row r="83" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>108</v>
+      </c>
+      <c r="Q83" s="1"/>
+      <c r="R83" s="1"/>
+      <c r="S83" s="1"/>
+      <c r="T83" s="1"/>
+      <c r="U83" s="1"/>
+      <c r="V83" s="1"/>
+      <c r="W83" s="1"/>
+      <c r="X83" s="1"/>
+      <c r="Y83" s="1"/>
+      <c r="Z83" s="1"/>
+      <c r="AA83" s="1"/>
+      <c r="AB83" s="1"/>
+      <c r="AC83" s="1"/>
+      <c r="AD83" s="1"/>
+      <c r="AE83" s="1"/>
+      <c r="AF83" s="1"/>
+      <c r="AG83" s="1"/>
+      <c r="AH83" s="1"/>
+      <c r="AI83" s="1"/>
+      <c r="AJ83" s="1"/>
+      <c r="AK83" s="1"/>
+      <c r="AL83" s="1"/>
+    </row>
+    <row r="84" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>109</v>
+      </c>
+      <c r="Q84" s="1"/>
+      <c r="R84" s="1"/>
+      <c r="S84" s="1"/>
+      <c r="T84" s="1"/>
+      <c r="U84" s="1"/>
+      <c r="V84" s="1"/>
+      <c r="W84" s="1"/>
+      <c r="X84" s="1"/>
+      <c r="Y84" s="1"/>
+      <c r="Z84" s="1"/>
+      <c r="AA84" s="1"/>
+      <c r="AB84" s="1"/>
+      <c r="AC84" s="1"/>
+      <c r="AD84" s="1"/>
+      <c r="AE84" s="1"/>
+      <c r="AF84" s="1"/>
+      <c r="AG84" s="1"/>
+      <c r="AH84" s="1"/>
+      <c r="AI84" s="1"/>
+      <c r="AJ84" s="1"/>
+      <c r="AK84" s="1"/>
+      <c r="AL84" s="1"/>
+    </row>
+    <row r="85" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>110</v>
+      </c>
+      <c r="Q85" s="1"/>
+      <c r="R85" s="1"/>
+      <c r="S85" s="1"/>
+      <c r="T85" s="1"/>
+      <c r="U85" s="1"/>
+      <c r="V85" s="1"/>
+      <c r="W85" s="1"/>
+      <c r="X85" s="1"/>
+      <c r="Y85" s="1"/>
+      <c r="Z85" s="1"/>
+      <c r="AA85" s="1"/>
+      <c r="AB85" s="1"/>
+      <c r="AC85" s="1"/>
+      <c r="AD85" s="1"/>
+      <c r="AE85" s="1"/>
+      <c r="AF85" s="1"/>
+      <c r="AG85" s="1"/>
+      <c r="AH85" s="1"/>
+      <c r="AI85" s="1"/>
+      <c r="AJ85" s="1"/>
+      <c r="AK85" s="1"/>
+      <c r="AL85" s="1"/>
+    </row>
+    <row r="86" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>111</v>
+      </c>
+      <c r="P86" s="1"/>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="1"/>
+      <c r="S86" s="1"/>
+      <c r="T86" s="1"/>
+      <c r="U86" s="1"/>
+      <c r="V86" s="1"/>
+      <c r="W86" s="1"/>
+      <c r="X86" s="1"/>
+      <c r="Y86" s="1"/>
+      <c r="Z86" s="1"/>
+      <c r="AA86" s="1"/>
+      <c r="AB86" s="1"/>
+      <c r="AC86" s="1"/>
+      <c r="AD86" s="1"/>
+      <c r="AE86" s="1"/>
+      <c r="AF86" s="1"/>
+      <c r="AG86" s="1"/>
+      <c r="AH86" s="1"/>
+      <c r="AI86" s="1"/>
+      <c r="AJ86" s="1"/>
+      <c r="AK86" s="1"/>
+      <c r="AL86" s="1"/>
+    </row>
+    <row r="87" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>112</v>
+      </c>
+      <c r="P87" s="1"/>
+      <c r="Q87" s="1"/>
+      <c r="R87" s="1"/>
+      <c r="S87" s="1"/>
+      <c r="T87" s="1"/>
+      <c r="U87" s="1"/>
+      <c r="V87" s="1"/>
+      <c r="W87" s="1"/>
+      <c r="X87" s="1"/>
+      <c r="Y87" s="1"/>
+      <c r="Z87" s="1"/>
+      <c r="AA87" s="1"/>
+      <c r="AB87" s="1"/>
+      <c r="AC87" s="1"/>
+      <c r="AD87" s="1"/>
+      <c r="AE87" s="1"/>
+      <c r="AF87" s="1"/>
+      <c r="AG87" s="1"/>
+      <c r="AH87" s="1"/>
+      <c r="AI87" s="1"/>
+      <c r="AJ87" s="1"/>
+      <c r="AK87" s="1"/>
+      <c r="AL87" s="1"/>
+    </row>
+    <row r="88" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>113</v>
+      </c>
+      <c r="P88" s="1"/>
+      <c r="Q88" s="1"/>
+      <c r="R88" s="1"/>
+      <c r="S88" s="1"/>
+      <c r="T88" s="1"/>
+      <c r="U88" s="1"/>
+      <c r="V88" s="1"/>
+      <c r="W88" s="1"/>
+      <c r="X88" s="1"/>
+      <c r="Y88" s="1"/>
+      <c r="Z88" s="1"/>
+      <c r="AA88" s="1"/>
+      <c r="AB88" s="1"/>
+      <c r="AC88" s="1"/>
+      <c r="AD88" s="1"/>
+      <c r="AE88" s="1"/>
+      <c r="AF88" s="1"/>
+      <c r="AG88" s="1"/>
+      <c r="AH88" s="1"/>
+      <c r="AI88" s="1"/>
+      <c r="AJ88" s="1"/>
+      <c r="AK88" s="1"/>
+      <c r="AL88" s="1"/>
+    </row>
+    <row r="89" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>114</v>
+      </c>
+      <c r="P89" s="1"/>
+      <c r="Q89" s="1"/>
+      <c r="R89" s="1"/>
+      <c r="S89" s="1"/>
+      <c r="T89" s="1"/>
+      <c r="U89" s="1"/>
+      <c r="V89" s="1"/>
+      <c r="W89" s="1"/>
+      <c r="X89" s="1"/>
+      <c r="Y89" s="1"/>
+      <c r="Z89" s="1"/>
+      <c r="AA89" s="1"/>
+      <c r="AB89" s="1"/>
+      <c r="AC89" s="1"/>
+      <c r="AD89" s="1"/>
+      <c r="AE89" s="1"/>
+      <c r="AF89" s="1"/>
+      <c r="AG89" s="1"/>
+      <c r="AH89" s="1"/>
+      <c r="AI89" s="1"/>
+      <c r="AJ89" s="1"/>
+      <c r="AK89" s="1"/>
+      <c r="AL89" s="1"/>
+    </row>
+    <row r="90" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>115</v>
+      </c>
+      <c r="O90" s="1"/>
+      <c r="P90" s="1"/>
+      <c r="Q90" s="1"/>
+      <c r="R90" s="1"/>
+      <c r="S90" s="1"/>
+      <c r="T90" s="1"/>
+      <c r="U90" s="1"/>
+      <c r="V90" s="1"/>
+      <c r="W90" s="1"/>
+      <c r="X90" s="1"/>
+      <c r="Y90" s="1"/>
+      <c r="Z90" s="1"/>
+      <c r="AA90" s="1"/>
+      <c r="AB90" s="1"/>
+      <c r="AC90" s="1"/>
+      <c r="AD90" s="1"/>
+      <c r="AE90" s="1"/>
+      <c r="AF90" s="1"/>
+      <c r="AG90" s="1"/>
+      <c r="AH90" s="1"/>
+      <c r="AI90" s="1"/>
+      <c r="AJ90" s="1"/>
+      <c r="AK90" s="1"/>
+      <c r="AL90" s="1"/>
+    </row>
+    <row r="91" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>116</v>
+      </c>
+      <c r="O91" s="1"/>
+      <c r="P91" s="1"/>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="1"/>
+      <c r="S91" s="1"/>
+      <c r="T91" s="1"/>
+      <c r="U91" s="1"/>
+      <c r="V91" s="1"/>
+      <c r="W91" s="1"/>
+      <c r="X91" s="1"/>
+      <c r="Y91" s="1"/>
+      <c r="Z91" s="1"/>
+      <c r="AA91" s="1"/>
+      <c r="AB91" s="1"/>
+      <c r="AC91" s="1"/>
+      <c r="AD91" s="1"/>
+      <c r="AE91" s="1"/>
+      <c r="AF91" s="1"/>
+      <c r="AG91" s="1"/>
+      <c r="AH91" s="1"/>
+      <c r="AI91" s="1"/>
+      <c r="AJ91" s="1"/>
+      <c r="AK91" s="1"/>
+      <c r="AL91" s="1"/>
+    </row>
+    <row r="92" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>117</v>
+      </c>
+      <c r="O92" s="1"/>
+      <c r="P92" s="1"/>
+      <c r="Q92" s="1"/>
+      <c r="R92" s="1"/>
+      <c r="S92" s="1"/>
+      <c r="T92" s="1"/>
+      <c r="U92" s="1"/>
+      <c r="V92" s="1"/>
+      <c r="W92" s="1"/>
+      <c r="X92" s="1"/>
+      <c r="Y92" s="1"/>
+      <c r="Z92" s="1"/>
+      <c r="AA92" s="1"/>
+      <c r="AB92" s="1"/>
+      <c r="AC92" s="1"/>
+      <c r="AD92" s="1"/>
+      <c r="AE92" s="1"/>
+      <c r="AF92" s="1"/>
+      <c r="AG92" s="1"/>
+      <c r="AH92" s="1"/>
+      <c r="AI92" s="1"/>
+      <c r="AJ92" s="1"/>
+      <c r="AK92" s="1"/>
+      <c r="AL92" s="1"/>
+    </row>
+    <row r="93" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>118</v>
+      </c>
+      <c r="O93" s="1"/>
+      <c r="P93" s="1"/>
+      <c r="Q93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="1"/>
+      <c r="U93" s="1"/>
+      <c r="V93" s="1"/>
+      <c r="W93" s="1"/>
+      <c r="X93" s="1"/>
+      <c r="Y93" s="1"/>
+      <c r="Z93" s="1"/>
+      <c r="AA93" s="1"/>
+      <c r="AB93" s="1"/>
+      <c r="AC93" s="1"/>
+      <c r="AD93" s="1"/>
+      <c r="AE93" s="1"/>
+      <c r="AF93" s="1"/>
+      <c r="AG93" s="1"/>
+      <c r="AH93" s="1"/>
+      <c r="AI93" s="1"/>
+      <c r="AJ93" s="1"/>
+      <c r="AK93" s="1"/>
+      <c r="AL93" s="1"/>
+    </row>
+    <row r="94" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>119</v>
+      </c>
+      <c r="O94" s="1"/>
+      <c r="P94" s="1"/>
+      <c r="Q94" s="1"/>
+      <c r="R94" s="1"/>
+      <c r="S94" s="1"/>
+      <c r="T94" s="1"/>
+      <c r="U94" s="1"/>
+      <c r="V94" s="1"/>
+      <c r="W94" s="1"/>
+      <c r="X94" s="1"/>
+      <c r="Y94" s="1"/>
+      <c r="Z94" s="1"/>
+      <c r="AA94" s="1"/>
+      <c r="AB94" s="1"/>
+      <c r="AC94" s="1"/>
+      <c r="AD94" s="1"/>
+      <c r="AE94" s="1"/>
+      <c r="AF94" s="1"/>
+      <c r="AG94" s="1"/>
+      <c r="AH94" s="1"/>
+      <c r="AI94" s="1"/>
+      <c r="AJ94" s="1"/>
+      <c r="AK94" s="1"/>
+      <c r="AL94" s="1"/>
+    </row>
+    <row r="95" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>120</v>
+      </c>
+      <c r="N95" s="1"/>
+      <c r="O95" s="1"/>
+      <c r="P95" s="1"/>
+      <c r="Q95" s="1"/>
+      <c r="R95" s="1"/>
+      <c r="S95" s="1"/>
+      <c r="T95" s="1"/>
+      <c r="U95" s="1"/>
+      <c r="V95" s="1"/>
+      <c r="W95" s="1"/>
+      <c r="X95" s="1"/>
+      <c r="Y95" s="1"/>
+      <c r="Z95" s="1"/>
+      <c r="AA95" s="1"/>
+      <c r="AB95" s="1"/>
+      <c r="AC95" s="1"/>
+      <c r="AD95" s="1"/>
+      <c r="AE95" s="1"/>
+      <c r="AF95" s="1"/>
+      <c r="AG95" s="1"/>
+      <c r="AH95" s="1"/>
+      <c r="AI95" s="1"/>
+      <c r="AJ95" s="1"/>
+      <c r="AK95" s="1"/>
+      <c r="AL95" s="1"/>
+    </row>
+    <row r="96" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>121</v>
+      </c>
+      <c r="N96" s="1"/>
+      <c r="O96" s="1"/>
+      <c r="P96" s="1"/>
+      <c r="Q96" s="1"/>
+      <c r="R96" s="1"/>
+      <c r="S96" s="1"/>
+      <c r="T96" s="1"/>
+      <c r="U96" s="1"/>
+      <c r="V96" s="1"/>
+      <c r="W96" s="1"/>
+      <c r="X96" s="1"/>
+      <c r="Y96" s="1"/>
+      <c r="Z96" s="1"/>
+      <c r="AA96" s="1"/>
+      <c r="AB96" s="1"/>
+      <c r="AC96" s="1"/>
+      <c r="AD96" s="1"/>
+      <c r="AE96" s="1"/>
+      <c r="AF96" s="1"/>
+      <c r="AG96" s="1"/>
+      <c r="AH96" s="1"/>
+      <c r="AI96" s="1"/>
+      <c r="AJ96" s="1"/>
+      <c r="AK96" s="1"/>
+      <c r="AL96" s="1"/>
+    </row>
+    <row r="97" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>122</v>
+      </c>
+      <c r="N97" s="1"/>
+      <c r="O97" s="1"/>
+      <c r="P97" s="1"/>
+      <c r="Q97" s="1"/>
+      <c r="R97" s="1"/>
+      <c r="S97" s="1"/>
+      <c r="T97" s="1"/>
+      <c r="U97" s="1"/>
+      <c r="V97" s="1"/>
+      <c r="W97" s="1"/>
+      <c r="X97" s="1"/>
+      <c r="Y97" s="1"/>
+      <c r="Z97" s="1"/>
+      <c r="AA97" s="1"/>
+      <c r="AB97" s="1"/>
+      <c r="AC97" s="1"/>
+      <c r="AD97" s="1"/>
+      <c r="AE97" s="1"/>
+      <c r="AF97" s="1"/>
+      <c r="AG97" s="1"/>
+      <c r="AH97" s="1"/>
+      <c r="AI97" s="1"/>
+      <c r="AJ97" s="1"/>
+      <c r="AK97" s="1"/>
+      <c r="AL97" s="1"/>
+    </row>
+    <row r="98" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>123</v>
+      </c>
+      <c r="N98" s="1"/>
+      <c r="O98" s="1"/>
+      <c r="P98" s="1"/>
+      <c r="Q98" s="1"/>
+      <c r="R98" s="1"/>
+      <c r="S98" s="1"/>
+      <c r="T98" s="1"/>
+      <c r="U98" s="1"/>
+      <c r="V98" s="1"/>
+      <c r="W98" s="1"/>
+      <c r="X98" s="1"/>
+      <c r="Y98" s="1"/>
+      <c r="Z98" s="1"/>
+      <c r="AA98" s="1"/>
+      <c r="AB98" s="1"/>
+      <c r="AC98" s="1"/>
+      <c r="AD98" s="1"/>
+      <c r="AE98" s="1"/>
+      <c r="AF98" s="1"/>
+      <c r="AG98" s="1"/>
+      <c r="AH98" s="1"/>
+      <c r="AI98" s="1"/>
+      <c r="AJ98" s="1"/>
+      <c r="AK98" s="1"/>
+      <c r="AL98" s="1"/>
+    </row>
+    <row r="99" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>124</v>
+      </c>
+      <c r="N99" s="1"/>
+      <c r="O99" s="1"/>
+      <c r="P99" s="1"/>
+      <c r="Q99" s="1"/>
+      <c r="R99" s="1"/>
+      <c r="S99" s="1"/>
+      <c r="T99" s="1"/>
+      <c r="U99" s="1"/>
+      <c r="V99" s="1"/>
+      <c r="W99" s="1"/>
+      <c r="X99" s="1"/>
+      <c r="Y99" s="1"/>
+      <c r="Z99" s="1"/>
+      <c r="AA99" s="1"/>
+      <c r="AB99" s="1"/>
+      <c r="AC99" s="1"/>
+      <c r="AD99" s="1"/>
+      <c r="AE99" s="1"/>
+      <c r="AF99" s="1"/>
+      <c r="AG99" s="1"/>
+      <c r="AH99" s="1"/>
+      <c r="AI99" s="1"/>
+      <c r="AJ99" s="1"/>
+      <c r="AK99" s="1"/>
+      <c r="AL99" s="1"/>
+    </row>
+    <row r="100" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>125</v>
+      </c>
+      <c r="M100" s="1"/>
+      <c r="N100" s="1"/>
+      <c r="O100" s="1"/>
+      <c r="P100" s="1"/>
+      <c r="Q100" s="1"/>
+      <c r="R100" s="1"/>
+      <c r="S100" s="1"/>
+      <c r="T100" s="1"/>
+      <c r="U100" s="1"/>
+      <c r="V100" s="1"/>
+      <c r="W100" s="1"/>
+      <c r="X100" s="1"/>
+      <c r="Y100" s="1"/>
+      <c r="Z100" s="1"/>
+      <c r="AA100" s="1"/>
+      <c r="AB100" s="1"/>
+      <c r="AC100" s="1"/>
+      <c r="AD100" s="1"/>
+      <c r="AE100" s="1"/>
+      <c r="AF100" s="1"/>
+      <c r="AG100" s="1"/>
+      <c r="AH100" s="1"/>
+      <c r="AI100" s="1"/>
+      <c r="AJ100" s="1"/>
+      <c r="AK100" s="1"/>
+      <c r="AL100" s="1"/>
+    </row>
+    <row r="101" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>126</v>
+      </c>
+      <c r="M101" s="1"/>
+      <c r="N101" s="1"/>
+      <c r="O101" s="1"/>
+      <c r="P101" s="1"/>
+      <c r="Q101" s="1"/>
+      <c r="R101" s="1"/>
+      <c r="S101" s="1"/>
+      <c r="T101" s="1"/>
+      <c r="U101" s="1"/>
+      <c r="V101" s="1"/>
+      <c r="W101" s="1"/>
+      <c r="X101" s="1"/>
+      <c r="Y101" s="1"/>
+      <c r="Z101" s="1"/>
+      <c r="AA101" s="1"/>
+      <c r="AB101" s="1"/>
+      <c r="AC101" s="1"/>
+      <c r="AD101" s="1"/>
+      <c r="AE101" s="1"/>
+      <c r="AF101" s="1"/>
+      <c r="AG101" s="1"/>
+      <c r="AH101" s="1"/>
+      <c r="AI101" s="1"/>
+      <c r="AJ101" s="1"/>
+      <c r="AK101" s="1"/>
+      <c r="AL101" s="1"/>
+    </row>
+    <row r="102" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>127</v>
+      </c>
+      <c r="M102" s="1"/>
+      <c r="N102" s="1"/>
+      <c r="O102" s="1"/>
+      <c r="P102" s="1"/>
+      <c r="Q102" s="1"/>
+      <c r="R102" s="1"/>
+      <c r="S102" s="1"/>
+      <c r="T102" s="1"/>
+      <c r="U102" s="1"/>
+      <c r="V102" s="1"/>
+      <c r="W102" s="1"/>
+      <c r="X102" s="1"/>
+      <c r="Y102" s="1"/>
+      <c r="Z102" s="1"/>
+      <c r="AA102" s="1"/>
+      <c r="AB102" s="1"/>
+      <c r="AC102" s="1"/>
+      <c r="AD102" s="1"/>
+      <c r="AE102" s="1"/>
+      <c r="AF102" s="1"/>
+      <c r="AG102" s="1"/>
+      <c r="AH102" s="1"/>
+      <c r="AI102" s="1"/>
+      <c r="AJ102" s="1"/>
+      <c r="AK102" s="1"/>
+      <c r="AL102" s="1"/>
+    </row>
+    <row r="103" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>128</v>
+      </c>
+      <c r="M103" s="1"/>
+      <c r="N103" s="1"/>
+      <c r="O103" s="1"/>
+      <c r="P103" s="1"/>
+      <c r="Q103" s="1"/>
+      <c r="R103" s="1"/>
+      <c r="S103" s="1"/>
+      <c r="T103" s="1"/>
+      <c r="U103" s="1"/>
+      <c r="V103" s="1"/>
+      <c r="W103" s="1"/>
+      <c r="X103" s="1"/>
+      <c r="Y103" s="1"/>
+      <c r="Z103" s="1"/>
+      <c r="AA103" s="1"/>
+      <c r="AB103" s="1"/>
+      <c r="AC103" s="1"/>
+      <c r="AD103" s="1"/>
+      <c r="AE103" s="1"/>
+      <c r="AF103" s="1"/>
+      <c r="AG103" s="1"/>
+      <c r="AH103" s="1"/>
+      <c r="AI103" s="1"/>
+      <c r="AJ103" s="1"/>
+      <c r="AK103" s="1"/>
+      <c r="AL103" s="1"/>
+    </row>
+    <row r="104" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>129</v>
+      </c>
+      <c r="L104" s="1"/>
+      <c r="M104" s="1"/>
+      <c r="N104" s="1"/>
+      <c r="O104" s="1"/>
+      <c r="P104" s="1"/>
+      <c r="Q104" s="1"/>
+      <c r="R104" s="1"/>
+      <c r="S104" s="1"/>
+      <c r="T104" s="1"/>
+      <c r="U104" s="1"/>
+      <c r="V104" s="1"/>
+      <c r="W104" s="1"/>
+      <c r="X104" s="1"/>
+      <c r="Y104" s="1"/>
+      <c r="Z104" s="1"/>
+      <c r="AA104" s="1"/>
+      <c r="AB104" s="1"/>
+      <c r="AC104" s="1"/>
+      <c r="AD104" s="1"/>
+      <c r="AE104" s="1"/>
+      <c r="AF104" s="1"/>
+      <c r="AG104" s="1"/>
+      <c r="AH104" s="1"/>
+      <c r="AI104" s="1"/>
+      <c r="AJ104" s="1"/>
+      <c r="AK104" s="1"/>
+      <c r="AL104" s="1"/>
+    </row>
+    <row r="105" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>130</v>
+      </c>
+      <c r="L105" s="1"/>
+      <c r="M105" s="1"/>
+      <c r="N105" s="1"/>
+      <c r="O105" s="1"/>
+      <c r="P105" s="1"/>
+      <c r="Q105" s="1"/>
+      <c r="R105" s="1"/>
+      <c r="S105" s="1"/>
+      <c r="T105" s="1"/>
+      <c r="U105" s="1"/>
+      <c r="V105" s="1"/>
+      <c r="W105" s="1"/>
+      <c r="X105" s="1"/>
+      <c r="Y105" s="1"/>
+      <c r="Z105" s="1"/>
+      <c r="AA105" s="1"/>
+      <c r="AB105" s="1"/>
+      <c r="AC105" s="1"/>
+      <c r="AD105" s="1"/>
+      <c r="AE105" s="1"/>
+      <c r="AF105" s="1"/>
+      <c r="AG105" s="1"/>
+      <c r="AH105" s="1"/>
+      <c r="AI105" s="1"/>
+      <c r="AJ105" s="1"/>
+      <c r="AK105" s="1"/>
+      <c r="AL105" s="1"/>
+    </row>
+    <row r="106" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>131</v>
+      </c>
+      <c r="K106" s="1"/>
+      <c r="L106" s="1"/>
+      <c r="M106" s="1"/>
+      <c r="N106" s="1"/>
+      <c r="O106" s="1"/>
+      <c r="P106" s="1"/>
+      <c r="Q106" s="1"/>
+      <c r="R106" s="1"/>
+      <c r="S106" s="1"/>
+      <c r="T106" s="1"/>
+      <c r="U106" s="1"/>
+      <c r="V106" s="1"/>
+      <c r="W106" s="1"/>
+      <c r="X106" s="1"/>
+      <c r="Y106" s="1"/>
+      <c r="Z106" s="1"/>
+      <c r="AA106" s="1"/>
+      <c r="AB106" s="1"/>
+      <c r="AC106" s="1"/>
+      <c r="AD106" s="1"/>
+      <c r="AE106" s="1"/>
+      <c r="AF106" s="1"/>
+      <c r="AG106" s="1"/>
+      <c r="AH106" s="1"/>
+      <c r="AI106" s="1"/>
+      <c r="AJ106" s="1"/>
+      <c r="AK106" s="1"/>
+      <c r="AL106" s="1"/>
+    </row>
+    <row r="107" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>132</v>
+      </c>
+      <c r="K107" s="1"/>
+      <c r="L107" s="1"/>
+      <c r="M107" s="1"/>
+      <c r="N107" s="1"/>
+      <c r="O107" s="1"/>
+      <c r="P107" s="1"/>
+      <c r="Q107" s="1"/>
+      <c r="R107" s="1"/>
+      <c r="S107" s="1"/>
+      <c r="T107" s="1"/>
+      <c r="U107" s="1"/>
+      <c r="V107" s="1"/>
+      <c r="W107" s="1"/>
+      <c r="X107" s="1"/>
+      <c r="Y107" s="1"/>
+      <c r="Z107" s="1"/>
+      <c r="AA107" s="1"/>
+      <c r="AB107" s="1"/>
+      <c r="AC107" s="1"/>
+      <c r="AD107" s="1"/>
+      <c r="AE107" s="1"/>
+      <c r="AF107" s="1"/>
+      <c r="AG107" s="1"/>
+      <c r="AH107" s="1"/>
+      <c r="AI107" s="1"/>
+      <c r="AJ107" s="1"/>
+      <c r="AK107" s="1"/>
+      <c r="AL107" s="1"/>
+    </row>
+    <row r="108" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>133</v>
+      </c>
+      <c r="K108" s="1"/>
+      <c r="L108" s="1"/>
+      <c r="M108" s="1"/>
+      <c r="N108" s="1"/>
+      <c r="O108" s="1"/>
+      <c r="P108" s="1"/>
+      <c r="Q108" s="1"/>
+      <c r="R108" s="1"/>
+      <c r="S108" s="1"/>
+      <c r="T108" s="1"/>
+      <c r="U108" s="1"/>
+      <c r="V108" s="1"/>
+      <c r="W108" s="1"/>
+      <c r="X108" s="1"/>
+      <c r="Y108" s="1"/>
+      <c r="Z108" s="1"/>
+      <c r="AA108" s="1"/>
+      <c r="AB108" s="1"/>
+      <c r="AC108" s="1"/>
+      <c r="AD108" s="1"/>
+      <c r="AE108" s="1"/>
+      <c r="AF108" s="1"/>
+      <c r="AG108" s="1"/>
+      <c r="AH108" s="1"/>
+      <c r="AI108" s="1"/>
+      <c r="AJ108" s="1"/>
+      <c r="AK108" s="1"/>
+      <c r="AL108" s="1"/>
+    </row>
+    <row r="109" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>134</v>
+      </c>
+      <c r="J109" s="1"/>
+      <c r="K109" s="1"/>
+      <c r="L109" s="1"/>
+      <c r="M109" s="1"/>
+      <c r="N109" s="1"/>
+      <c r="O109" s="1"/>
+      <c r="P109" s="1"/>
+      <c r="Q109" s="1"/>
+      <c r="R109" s="1"/>
+      <c r="S109" s="1"/>
+      <c r="T109" s="1"/>
+      <c r="U109" s="1"/>
+      <c r="V109" s="1"/>
+      <c r="W109" s="1"/>
+      <c r="X109" s="1"/>
+      <c r="Y109" s="1"/>
+      <c r="Z109" s="1"/>
+      <c r="AA109" s="1"/>
+      <c r="AB109" s="1"/>
+      <c r="AC109" s="1"/>
+      <c r="AD109" s="1"/>
+      <c r="AE109" s="1"/>
+      <c r="AF109" s="1"/>
+      <c r="AG109" s="1"/>
+      <c r="AH109" s="1"/>
+      <c r="AI109" s="1"/>
+      <c r="AJ109" s="1"/>
+      <c r="AK109" s="1"/>
+      <c r="AL109" s="1"/>
+    </row>
+    <row r="110" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>135</v>
+      </c>
+      <c r="J110" s="1"/>
+      <c r="K110" s="1"/>
+      <c r="L110" s="1"/>
+      <c r="M110" s="1"/>
+      <c r="N110" s="1"/>
+      <c r="O110" s="1"/>
+      <c r="P110" s="1"/>
+      <c r="Q110" s="1"/>
+      <c r="R110" s="1"/>
+      <c r="S110" s="1"/>
+      <c r="T110" s="1"/>
+      <c r="U110" s="1"/>
+      <c r="V110" s="1"/>
+      <c r="W110" s="1"/>
+      <c r="X110" s="1"/>
+      <c r="Y110" s="1"/>
+      <c r="Z110" s="1"/>
+      <c r="AA110" s="1"/>
+      <c r="AB110" s="1"/>
+      <c r="AC110" s="1"/>
+      <c r="AD110" s="1"/>
+      <c r="AE110" s="1"/>
+      <c r="AF110" s="1"/>
+      <c r="AG110" s="1"/>
+      <c r="AH110" s="1"/>
+      <c r="AI110" s="1"/>
+      <c r="AJ110" s="1"/>
+      <c r="AK110" s="1"/>
+      <c r="AL110" s="1"/>
+    </row>
+    <row r="111" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>136</v>
+      </c>
+      <c r="J111" s="1"/>
+      <c r="K111" s="1"/>
+      <c r="L111" s="1"/>
+      <c r="M111" s="1"/>
+      <c r="N111" s="1"/>
+      <c r="O111" s="1"/>
+      <c r="P111" s="1"/>
+      <c r="Q111" s="1"/>
+      <c r="R111" s="1"/>
+      <c r="S111" s="1"/>
+      <c r="T111" s="1"/>
+      <c r="U111" s="1"/>
+      <c r="V111" s="1"/>
+      <c r="W111" s="1"/>
+      <c r="X111" s="1"/>
+      <c r="Y111" s="1"/>
+      <c r="Z111" s="1"/>
+      <c r="AA111" s="1"/>
+      <c r="AB111" s="1"/>
+      <c r="AC111" s="1"/>
+      <c r="AD111" s="1"/>
+      <c r="AE111" s="1"/>
+      <c r="AF111" s="1"/>
+      <c r="AG111" s="1"/>
+      <c r="AH111" s="1"/>
+      <c r="AI111" s="1"/>
+      <c r="AJ111" s="1"/>
+      <c r="AK111" s="1"/>
+      <c r="AL111" s="1"/>
+    </row>
+    <row r="112" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>137</v>
+      </c>
+      <c r="I112" s="1"/>
+      <c r="J112" s="1"/>
+      <c r="K112" s="1"/>
+      <c r="L112" s="1"/>
+      <c r="M112" s="1"/>
+      <c r="N112" s="1"/>
+      <c r="O112" s="1"/>
+      <c r="P112" s="1"/>
+      <c r="Q112" s="1"/>
+      <c r="R112" s="1"/>
+      <c r="S112" s="1"/>
+      <c r="T112" s="1"/>
+      <c r="U112" s="1"/>
+      <c r="V112" s="1"/>
+      <c r="W112" s="1"/>
+      <c r="X112" s="1"/>
+      <c r="Y112" s="1"/>
+      <c r="Z112" s="1"/>
+      <c r="AA112" s="1"/>
+      <c r="AB112" s="1"/>
+      <c r="AC112" s="1"/>
+      <c r="AD112" s="1"/>
+      <c r="AE112" s="1"/>
+      <c r="AF112" s="1"/>
+      <c r="AG112" s="1"/>
+      <c r="AH112" s="1"/>
+      <c r="AI112" s="1"/>
+      <c r="AJ112" s="1"/>
+      <c r="AK112" s="1"/>
+      <c r="AL112" s="1"/>
+    </row>
+    <row r="113" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>138</v>
+      </c>
+      <c r="I113" s="1"/>
+      <c r="J113" s="1"/>
+      <c r="K113" s="1"/>
+      <c r="L113" s="1"/>
+      <c r="M113" s="1"/>
+      <c r="N113" s="1"/>
+      <c r="O113" s="1"/>
+      <c r="P113" s="1"/>
+      <c r="Q113" s="1"/>
+      <c r="R113" s="1"/>
+      <c r="S113" s="1"/>
+      <c r="T113" s="1"/>
+      <c r="U113" s="1"/>
+      <c r="V113" s="1"/>
+      <c r="W113" s="1"/>
+      <c r="X113" s="1"/>
+      <c r="Y113" s="1"/>
+      <c r="Z113" s="1"/>
+      <c r="AA113" s="1"/>
+      <c r="AB113" s="1"/>
+      <c r="AC113" s="1"/>
+      <c r="AD113" s="1"/>
+      <c r="AE113" s="1"/>
+      <c r="AF113" s="1"/>
+      <c r="AG113" s="1"/>
+      <c r="AH113" s="1"/>
+      <c r="AI113" s="1"/>
+      <c r="AJ113" s="1"/>
+      <c r="AK113" s="1"/>
+      <c r="AL113" s="1"/>
+    </row>
+    <row r="114" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>139</v>
+      </c>
+      <c r="I114" s="1"/>
+      <c r="J114" s="1"/>
+      <c r="K114" s="1"/>
+      <c r="L114" s="1"/>
+      <c r="M114" s="1"/>
+      <c r="N114" s="1"/>
+      <c r="O114" s="1"/>
+      <c r="P114" s="1"/>
+      <c r="Q114" s="1"/>
+      <c r="R114" s="1"/>
+      <c r="S114" s="1"/>
+      <c r="T114" s="1"/>
+      <c r="U114" s="1"/>
+      <c r="V114" s="1"/>
+      <c r="W114" s="1"/>
+      <c r="X114" s="1"/>
+      <c r="Y114" s="1"/>
+      <c r="Z114" s="1"/>
+      <c r="AA114" s="1"/>
+      <c r="AB114" s="1"/>
+      <c r="AC114" s="1"/>
+      <c r="AD114" s="1"/>
+      <c r="AE114" s="1"/>
+      <c r="AF114" s="1"/>
+      <c r="AG114" s="1"/>
+      <c r="AH114" s="1"/>
+      <c r="AI114" s="1"/>
+      <c r="AJ114" s="1"/>
+      <c r="AK114" s="1"/>
+      <c r="AL114" s="1"/>
+    </row>
+    <row r="115" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>140</v>
+      </c>
+      <c r="H115" s="1"/>
+      <c r="I115" s="1"/>
+      <c r="J115" s="1"/>
+      <c r="K115" s="1"/>
+      <c r="L115" s="1"/>
+      <c r="M115" s="1"/>
+      <c r="N115" s="1"/>
+      <c r="O115" s="1"/>
+      <c r="P115" s="1"/>
+      <c r="Q115" s="1"/>
+      <c r="R115" s="1"/>
+      <c r="S115" s="1"/>
+      <c r="T115" s="1"/>
+      <c r="U115" s="1"/>
+      <c r="V115" s="1"/>
+      <c r="W115" s="1"/>
+      <c r="X115" s="1"/>
+      <c r="Y115" s="1"/>
+      <c r="Z115" s="1"/>
+      <c r="AA115" s="1"/>
+      <c r="AB115" s="1"/>
+      <c r="AC115" s="1"/>
+      <c r="AD115" s="1"/>
+      <c r="AE115" s="1"/>
+      <c r="AF115" s="1"/>
+      <c r="AG115" s="1"/>
+      <c r="AH115" s="1"/>
+      <c r="AI115" s="1"/>
+      <c r="AJ115" s="1"/>
+      <c r="AK115" s="1"/>
+      <c r="AL115" s="1"/>
+    </row>
+    <row r="116" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>141</v>
+      </c>
+      <c r="H116" s="1"/>
+      <c r="I116" s="1"/>
+      <c r="J116" s="1"/>
+      <c r="K116" s="1"/>
+      <c r="L116" s="1"/>
+      <c r="M116" s="1"/>
+      <c r="N116" s="1"/>
+      <c r="O116" s="1"/>
+      <c r="P116" s="1"/>
+      <c r="Q116" s="1"/>
+      <c r="R116" s="1"/>
+      <c r="S116" s="1"/>
+      <c r="T116" s="1"/>
+      <c r="U116" s="1"/>
+      <c r="V116" s="1"/>
+      <c r="W116" s="1"/>
+      <c r="X116" s="1"/>
+      <c r="Y116" s="1"/>
+      <c r="Z116" s="1"/>
+      <c r="AA116" s="1"/>
+      <c r="AB116" s="1"/>
+      <c r="AC116" s="1"/>
+      <c r="AD116" s="1"/>
+      <c r="AE116" s="1"/>
+      <c r="AF116" s="1"/>
+      <c r="AG116" s="1"/>
+      <c r="AH116" s="1"/>
+      <c r="AI116" s="1"/>
+      <c r="AJ116" s="1"/>
+      <c r="AK116" s="1"/>
+      <c r="AL116" s="1"/>
+    </row>
+    <row r="117" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>142</v>
+      </c>
+      <c r="G117" s="1"/>
+      <c r="H117" s="1"/>
+      <c r="I117" s="1"/>
+      <c r="J117" s="1"/>
+      <c r="K117" s="1"/>
+      <c r="L117" s="1"/>
+      <c r="M117" s="1"/>
+      <c r="N117" s="1"/>
+      <c r="O117" s="1"/>
+      <c r="P117" s="1"/>
+      <c r="Q117" s="1"/>
+      <c r="R117" s="1"/>
+      <c r="S117" s="1"/>
+      <c r="T117" s="1"/>
+      <c r="U117" s="1"/>
+      <c r="V117" s="1"/>
+      <c r="W117" s="1"/>
+      <c r="X117" s="1"/>
+      <c r="Y117" s="1"/>
+      <c r="Z117" s="1"/>
+      <c r="AA117" s="1"/>
+      <c r="AB117" s="1"/>
+      <c r="AC117" s="1"/>
+      <c r="AD117" s="1"/>
+      <c r="AE117" s="1"/>
+      <c r="AF117" s="1"/>
+      <c r="AG117" s="1"/>
+      <c r="AH117" s="1"/>
+      <c r="AI117" s="1"/>
+      <c r="AJ117" s="1"/>
+      <c r="AK117" s="1"/>
+      <c r="AL117" s="1"/>
+    </row>
+    <row r="118" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>143</v>
+      </c>
+      <c r="G118" s="1"/>
+      <c r="H118" s="1"/>
+      <c r="I118" s="1"/>
+      <c r="J118" s="1"/>
+      <c r="K118" s="1"/>
+      <c r="L118" s="1"/>
+      <c r="M118" s="1"/>
+      <c r="N118" s="1"/>
+      <c r="O118" s="1"/>
+      <c r="P118" s="1"/>
+      <c r="Q118" s="1"/>
+      <c r="R118" s="1"/>
+      <c r="S118" s="1"/>
+      <c r="T118" s="1"/>
+      <c r="U118" s="1"/>
+      <c r="V118" s="1"/>
+      <c r="W118" s="1"/>
+      <c r="X118" s="1"/>
+      <c r="Y118" s="1"/>
+      <c r="Z118" s="1"/>
+      <c r="AA118" s="1"/>
+      <c r="AB118" s="1"/>
+      <c r="AC118" s="1"/>
+      <c r="AD118" s="1"/>
+      <c r="AE118" s="1"/>
+      <c r="AF118" s="1"/>
+      <c r="AG118" s="1"/>
+      <c r="AH118" s="1"/>
+      <c r="AI118" s="1"/>
+      <c r="AJ118" s="1"/>
+      <c r="AK118" s="1"/>
+      <c r="AL118" s="1"/>
+    </row>
+    <row r="119" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>144</v>
+      </c>
+      <c r="G119" s="1"/>
+      <c r="H119" s="1"/>
+      <c r="I119" s="1"/>
+      <c r="J119" s="1"/>
+      <c r="K119" s="1"/>
+      <c r="L119" s="1"/>
+      <c r="M119" s="1"/>
+      <c r="N119" s="1"/>
+      <c r="O119" s="1"/>
+      <c r="P119" s="1"/>
+      <c r="Q119" s="1"/>
+      <c r="R119" s="1"/>
+      <c r="S119" s="1"/>
+      <c r="T119" s="1"/>
+      <c r="U119" s="1"/>
+      <c r="V119" s="1"/>
+      <c r="W119" s="1"/>
+      <c r="X119" s="1"/>
+      <c r="Y119" s="1"/>
+      <c r="Z119" s="1"/>
+      <c r="AA119" s="1"/>
+      <c r="AB119" s="1"/>
+      <c r="AC119" s="1"/>
+      <c r="AD119" s="1"/>
+      <c r="AE119" s="1"/>
+      <c r="AF119" s="1"/>
+      <c r="AG119" s="1"/>
+      <c r="AH119" s="1"/>
+      <c r="AI119" s="1"/>
+      <c r="AJ119" s="1"/>
+      <c r="AK119" s="1"/>
+      <c r="AL119" s="1"/>
+    </row>
+    <row r="120" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>145</v>
+      </c>
+      <c r="F120" s="1"/>
+      <c r="G120" s="1"/>
+      <c r="H120" s="1"/>
+      <c r="I120" s="1"/>
+      <c r="J120" s="1"/>
+      <c r="K120" s="1"/>
+      <c r="L120" s="1"/>
+      <c r="M120" s="1"/>
+      <c r="N120" s="1"/>
+      <c r="O120" s="1"/>
+      <c r="P120" s="1"/>
+      <c r="Q120" s="1"/>
+      <c r="R120" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="T120" s="1"/>
+      <c r="U120" s="1"/>
+      <c r="V120" s="1"/>
+      <c r="W120" s="1"/>
+      <c r="X120" s="1"/>
+      <c r="Y120" s="1"/>
+      <c r="Z120" s="1"/>
+      <c r="AA120" s="1"/>
+      <c r="AB120" s="1"/>
+      <c r="AC120" s="1"/>
+      <c r="AD120" s="1"/>
+      <c r="AE120" s="1"/>
+      <c r="AF120" s="1"/>
+      <c r="AG120" s="1"/>
+      <c r="AH120" s="1"/>
+      <c r="AI120" s="1"/>
+      <c r="AJ120" s="1"/>
+      <c r="AK120" s="1"/>
+      <c r="AL120" s="1"/>
+    </row>
+    <row r="121" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>146</v>
+      </c>
+      <c r="F121" s="1"/>
+      <c r="G121" s="1"/>
+      <c r="H121" s="1"/>
+      <c r="I121" s="1"/>
+      <c r="J121" s="1"/>
+      <c r="K121" s="1"/>
+      <c r="L121" s="1"/>
+      <c r="M121" s="1"/>
+      <c r="N121" s="1"/>
+      <c r="O121" s="1"/>
+      <c r="P121" s="1"/>
+      <c r="Q121" s="1"/>
+      <c r="R121" s="1"/>
+      <c r="S121" s="1"/>
+      <c r="T121" s="1"/>
+      <c r="U121" s="1"/>
+      <c r="V121" s="1"/>
+      <c r="W121" s="1"/>
+      <c r="X121" s="1"/>
+      <c r="Y121" s="1"/>
+      <c r="Z121" s="1"/>
+      <c r="AA121" s="1"/>
+      <c r="AB121" s="1"/>
+      <c r="AC121" s="1"/>
+      <c r="AD121" s="1"/>
+      <c r="AE121" s="1"/>
+      <c r="AF121" s="1"/>
+      <c r="AG121" s="1"/>
+      <c r="AH121" s="1"/>
+      <c r="AI121" s="1"/>
+      <c r="AJ121" s="1"/>
+      <c r="AK121" s="1"/>
+      <c r="AL121" s="1"/>
+    </row>
+    <row r="122" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>147</v>
+      </c>
+      <c r="F122" s="1"/>
+      <c r="G122" s="1"/>
+      <c r="H122" s="1"/>
+      <c r="I122" s="1"/>
+      <c r="J122" s="1"/>
+      <c r="K122" s="1"/>
+      <c r="L122" s="1"/>
+      <c r="M122" s="1"/>
+      <c r="N122" s="1"/>
+      <c r="O122" s="1"/>
+      <c r="P122" s="1"/>
+      <c r="Q122" s="1"/>
+      <c r="R122" s="1"/>
+      <c r="S122" s="1"/>
+      <c r="T122" s="1"/>
+      <c r="U122" s="1"/>
+      <c r="V122" s="1"/>
+      <c r="W122" s="1"/>
+      <c r="X122" s="1"/>
+      <c r="Y122" s="1"/>
+      <c r="Z122" s="1"/>
+      <c r="AA122" s="1"/>
+      <c r="AB122" s="1"/>
+      <c r="AC122" s="1"/>
+      <c r="AD122" s="1"/>
+      <c r="AE122" s="1"/>
+      <c r="AF122" s="1"/>
+      <c r="AG122" s="1"/>
+      <c r="AH122" s="1"/>
+      <c r="AI122" s="1"/>
+      <c r="AJ122" s="1"/>
+      <c r="AK122" s="1"/>
+      <c r="AL122" s="1"/>
+    </row>
+    <row r="123" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>148</v>
+      </c>
+      <c r="E123" s="1"/>
+      <c r="F123" s="1"/>
+      <c r="G123" s="1"/>
+      <c r="H123" s="1"/>
+      <c r="I123" s="1"/>
+      <c r="J123" s="1"/>
+      <c r="K123" s="1"/>
+      <c r="L123" s="1"/>
+      <c r="M123" s="1"/>
+      <c r="N123" s="1"/>
+      <c r="O123" s="1"/>
+      <c r="P123" s="1"/>
+      <c r="Q123" s="1"/>
+      <c r="R123" s="1"/>
+      <c r="S123" s="1"/>
+      <c r="T123" s="1"/>
+      <c r="U123" s="1"/>
+      <c r="V123" s="1"/>
+      <c r="W123" s="1"/>
+      <c r="X123" s="1"/>
+      <c r="Y123" s="1"/>
+      <c r="Z123" s="1"/>
+      <c r="AA123" s="1"/>
+      <c r="AB123" s="1"/>
+      <c r="AC123" s="1"/>
+      <c r="AD123" s="1"/>
+      <c r="AE123" s="1"/>
+      <c r="AF123" s="1"/>
+      <c r="AG123" s="1"/>
+      <c r="AH123" s="1"/>
+      <c r="AI123" s="1"/>
+      <c r="AJ123" s="1"/>
+      <c r="AK123" s="1"/>
+      <c r="AL123" s="1"/>
+    </row>
+    <row r="124" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>149</v>
+      </c>
+      <c r="E124" s="1"/>
+      <c r="F124" s="1"/>
+      <c r="G124" s="1"/>
+      <c r="H124" s="1"/>
+      <c r="I124" s="1"/>
+      <c r="J124" s="1"/>
+      <c r="K124" s="1"/>
+      <c r="L124" s="1"/>
+      <c r="M124" s="1"/>
+      <c r="N124" s="1"/>
+      <c r="O124" s="1"/>
+      <c r="P124" s="1"/>
+      <c r="Q124" s="1"/>
+      <c r="R124" s="1"/>
+      <c r="S124" s="1"/>
+      <c r="T124" s="1"/>
+      <c r="U124" s="1"/>
+      <c r="V124" s="1"/>
+      <c r="W124" s="1"/>
+      <c r="X124" s="1"/>
+      <c r="Y124" s="1"/>
+      <c r="Z124" s="1"/>
+      <c r="AA124" s="1"/>
+      <c r="AB124" s="1"/>
+      <c r="AC124" s="1"/>
+      <c r="AD124" s="1"/>
+      <c r="AE124" s="1"/>
+      <c r="AF124" s="1"/>
+      <c r="AG124" s="1"/>
+      <c r="AH124" s="1"/>
+      <c r="AI124" s="1"/>
+      <c r="AJ124" s="1"/>
+      <c r="AK124" s="1"/>
+      <c r="AL124" s="1"/>
+    </row>
+    <row r="125" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>150</v>
+      </c>
+      <c r="E125" s="1"/>
+      <c r="F125" s="1"/>
+      <c r="G125" s="1"/>
+      <c r="H125" s="1"/>
+      <c r="I125" s="1"/>
+      <c r="J125" s="1"/>
+      <c r="K125" s="1"/>
+      <c r="L125" s="1"/>
+      <c r="M125" s="1"/>
+      <c r="N125" s="1"/>
+      <c r="O125" s="1"/>
+      <c r="P125" s="1"/>
+      <c r="Q125" s="1"/>
+      <c r="R125" s="1"/>
+      <c r="S125" s="1"/>
+      <c r="T125" s="1"/>
+      <c r="U125" s="1"/>
+      <c r="V125" s="1"/>
+      <c r="W125" s="1"/>
+      <c r="X125" s="1"/>
+      <c r="Y125" s="1"/>
+      <c r="Z125" s="1"/>
+      <c r="AA125" s="1"/>
+      <c r="AB125" s="1"/>
+      <c r="AC125" s="1"/>
+      <c r="AD125" s="1"/>
+      <c r="AE125" s="1"/>
+      <c r="AF125" s="1"/>
+      <c r="AG125" s="1"/>
+      <c r="AH125" s="1"/>
+      <c r="AI125" s="1"/>
+      <c r="AJ125" s="1"/>
+      <c r="AK125" s="1"/>
+      <c r="AL125" s="1"/>
+    </row>
+    <row r="126" spans="1:38" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>151</v>
+      </c>
+      <c r="D126" s="1"/>
+      <c r="E126" s="1"/>
+      <c r="F126" s="1"/>
+      <c r="G126" s="1"/>
+      <c r="H126" s="1"/>
+      <c r="I126" s="1"/>
+      <c r="J126" s="1"/>
+      <c r="K126" s="1"/>
+      <c r="L126" s="1"/>
+      <c r="M126" s="1"/>
+      <c r="N126" s="1"/>
+      <c r="O126" s="1"/>
+      <c r="P126" s="1"/>
+      <c r="Q126" s="1"/>
+      <c r="R126" s="1"/>
+      <c r="S126" s="1"/>
+      <c r="T126" s="1"/>
+      <c r="U126" s="1"/>
+      <c r="V126" s="1"/>
+      <c r="W126" s="1"/>
+      <c r="X126" s="1"/>
+      <c r="Y126" s="1"/>
+      <c r="Z126" s="1"/>
+      <c r="AA126" s="1"/>
+      <c r="AB126" s="1"/>
+      <c r="AC126" s="1"/>
+      <c r="AD126" s="1"/>
+      <c r="AE126" s="1"/>
+      <c r="AF126" s="1"/>
+      <c r="AG126" s="1"/>
+      <c r="AH126" s="1"/>
+      <c r="AI126" s="1"/>
+      <c r="AJ126" s="1"/>
+      <c r="AK126" s="1"/>
+      <c r="AL126" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1602,7 +5216,7 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7053FD00-70E4-44ED-874D-48591AC61FE1}">
-  <dimension ref="A1:S23"/>
+  <dimension ref="A1:S24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.28515625" bestFit="1" customWidth="1"/>
@@ -1676,16 +5290,7 @@
       </c>
       <c r="B2">
         <f>SUM(C2:C2:S2)</f>
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -1694,16 +5299,7 @@
       </c>
       <c r="B3">
         <f>SUM(C3:C3:S3)</f>
-        <v>3</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -1712,16 +5308,7 @@
       </c>
       <c r="B4">
         <f>SUM(C4:C4:S4)</f>
-        <v>3</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -1730,16 +5317,7 @@
       </c>
       <c r="B5">
         <f>SUM(C5:C5:S5)</f>
-        <v>3</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -1748,16 +5326,7 @@
       </c>
       <c r="B6">
         <f>SUM(C6:C6:S6)</f>
-        <v>3</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -1766,16 +5335,7 @@
       </c>
       <c r="B7">
         <f>SUM(C7:C7:S7)</f>
-        <v>3</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -1784,16 +5344,7 @@
       </c>
       <c r="B8">
         <f>SUM(C8:C8:S8)</f>
-        <v>3</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -1802,16 +5353,7 @@
       </c>
       <c r="B9">
         <f>SUM(C9:C9:S9)</f>
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:19" x14ac:dyDescent="0.25">
@@ -1820,16 +5362,7 @@
       </c>
       <c r="B10">
         <f>SUM(C10:C10:S10)</f>
-        <v>3</v>
-      </c>
-      <c r="C10">
-        <v>1</v>
-      </c>
-      <c r="D10">
-        <v>1</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:19" x14ac:dyDescent="0.25">
@@ -1838,16 +5371,7 @@
       </c>
       <c r="B11">
         <f>SUM(C11:C11:S11)</f>
-        <v>3</v>
-      </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
-      <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:19" x14ac:dyDescent="0.25">
@@ -1856,16 +5380,7 @@
       </c>
       <c r="B12">
         <f>SUM(C12:C12:S12)</f>
-        <v>3</v>
-      </c>
-      <c r="C12">
-        <v>1</v>
-      </c>
-      <c r="D12">
-        <v>1</v>
-      </c>
-      <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:19" x14ac:dyDescent="0.25">
@@ -1874,16 +5389,7 @@
       </c>
       <c r="B13">
         <f>SUM(C13:C13:S13)</f>
-        <v>3</v>
-      </c>
-      <c r="C13">
-        <v>1</v>
-      </c>
-      <c r="D13">
-        <v>1</v>
-      </c>
-      <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:19" x14ac:dyDescent="0.25">
@@ -1892,16 +5398,7 @@
       </c>
       <c r="B14">
         <f>SUM(C14:C14:S14)</f>
-        <v>3</v>
-      </c>
-      <c r="C14">
-        <v>1</v>
-      </c>
-      <c r="D14">
-        <v>1</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:19" x14ac:dyDescent="0.25">
@@ -1910,16 +5407,7 @@
       </c>
       <c r="B15">
         <f>SUM(C15:C15:S15)</f>
-        <v>3</v>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>1</v>
-      </c>
-      <c r="E15">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:19" x14ac:dyDescent="0.25">
@@ -1928,142 +5416,79 @@
       </c>
       <c r="B16">
         <f>SUM(C16:C16:S16)</f>
-        <v>3</v>
-      </c>
-      <c r="C16">
-        <v>1</v>
-      </c>
-      <c r="D16">
-        <v>1</v>
-      </c>
-      <c r="E16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>17</v>
       </c>
       <c r="B17">
         <f>SUM(C17:C17:S17)</f>
-        <v>3</v>
-      </c>
-      <c r="C17">
-        <v>1</v>
-      </c>
-      <c r="D17">
-        <v>1</v>
-      </c>
-      <c r="E17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>18</v>
       </c>
       <c r="B18">
         <f>SUM(C18:C18:S18)</f>
-        <v>3</v>
-      </c>
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>1</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>19</v>
+        <v>53</v>
       </c>
       <c r="B19">
         <f>SUM(C19:C19:S19)</f>
-        <v>3</v>
-      </c>
-      <c r="C19">
-        <v>1</v>
-      </c>
-      <c r="D19">
-        <v>1</v>
-      </c>
-      <c r="E19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B20">
         <f>SUM(C20:C20:S20)</f>
-        <v>2</v>
-      </c>
-      <c r="C20">
         <v>0</v>
       </c>
-      <c r="D20">
-        <v>1</v>
-      </c>
-      <c r="E20">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21">
         <f>SUM(C21:C21:S21)</f>
-        <v>2</v>
-      </c>
-      <c r="C21">
         <v>0</v>
       </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
         <f>SUM(C22:C22:S22)</f>
-        <v>3</v>
-      </c>
-      <c r="C22">
-        <v>1</v>
-      </c>
-      <c r="D22">
-        <v>1</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
         <f>SUM(C23:C23:S23)</f>
-        <v>3</v>
-      </c>
-      <c r="C23">
-        <v>1</v>
-      </c>
-      <c r="D23">
-        <v>1</v>
-      </c>
-      <c r="E23">
-        <v>1</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>23</v>
+      </c>
+      <c r="B24">
+        <f>SUM(C24:C24:S24)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +5498,7 @@
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5D4303C-7F1D-4CBD-BF56-16C815E789BE}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B25"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
@@ -2095,17 +5520,158 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>62</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E80DB57-1D34-4995-8AA7-BD186A2BDBE8}">
+  <dimension ref="A1:B26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -2115,82 +5681,669 @@
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>45</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>46</v>
+        <v>60</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>18</v>
+        <v>63</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>48</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>11</v>
+        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>67</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95F0FCB7-825F-41B0-8DBE-275FB691B4D1}">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>74</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C60C079E-583C-4AF5-A6A9-C3E86F60AFD7}">
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>80</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B9C6E86-EC8A-4EA5-A30B-4A7F0858E0A5}">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5342EC0-9A20-4134-BF81-DC6CEEC14B92}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -2321,6 +6474,1381 @@
       </c>
       <c r="R2">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F76B976-1DE3-4828-AFA3-C2C8CE6A8C8D}">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>93</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9FD15434-4874-452F-8199-FC863C296E8B}">
+  <dimension ref="A1:A28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B951F07-E9BC-4825-9AA7-DCA2D6A9E9B8}">
+  <dimension ref="A1:A29"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>96</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8ED86059-0F40-42A6-AE6A-E4A8243B3C21}">
+  <dimension ref="A1:A26"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>16</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B828EF67-0DDF-4C73-BB7C-135261ED3818}">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="19" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>110</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7D05EA9-09C8-45DF-9887-5028388B0199}">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AB2F14C-4266-4398-862F-517EC6F2BF68}">
+  <dimension ref="A1:A22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D9081B27-A4FF-4FDB-A545-8BEAAEB98497}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>124</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D47B59A-B1BE-4472-A7E7-70223D1707FA}">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F202A74-DE9C-4BEE-9BC5-F661CBB67E18}">
+  <dimension ref="A1:A21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -2459,6 +7987,1027 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B5FA89E6-064E-4CAF-91E1-B8698E14C23C}">
+  <dimension ref="A1:A21"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>133</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7743BE8-494B-4549-A27B-0B0C0DC916B8}">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>136</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56826E7E-7CC5-4FC4-AA7B-870479195203}">
+  <dimension ref="A1:A22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>139</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C16F4FE-A52D-4398-8BE4-A0ECC46C9962}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>95</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A16EA40-13C9-4D0C-A228-ED069B0DFCDE}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>141</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{17A1C5AB-79A4-4A2A-A59C-9F1C1089C3B0}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DC85092-DD56-4DFB-A3DE-A66B323B833F}">
+  <dimension ref="A1:A22"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>147</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{194B9004-BFC1-4A04-AEDF-CD50347CD713}">
+  <dimension ref="A1:A23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="16" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>125</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0D2BC23-0382-4C73-BD55-9C5BF90A5872}">
   <dimension ref="A1:R4"/>
@@ -2705,58 +9254,163 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EBD508AD-7632-48CF-B894-9F6914C08CD8}">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>51</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>31</v>
+      </c>
+      <c r="G1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>41</v>
+      </c>
+      <c r="R1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B2">
+        <f>SUM(C2:R2)</f>
+        <v>1</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <f t="shared" ref="B3:B9" si="0">SUM(C3:R3)</f>
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>48</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2766,15 +9420,558 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1668A00-6C37-4B7D-B869-26E922968418}">
-  <dimension ref="A1"/>
+  <dimension ref="A1:S9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E1" t="s">
+        <v>28</v>
+      </c>
+      <c r="F1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" t="s">
+        <v>32</v>
+      </c>
+      <c r="I1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J1" t="s">
+        <v>34</v>
+      </c>
+      <c r="K1" t="s">
+        <v>36</v>
+      </c>
+      <c r="L1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M1" t="s">
+        <v>38</v>
+      </c>
+      <c r="N1" t="s">
+        <v>39</v>
+      </c>
+      <c r="O1" t="s">
+        <v>43</v>
+      </c>
+      <c r="P1" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>51</v>
+      </c>
+      <c r="R1" t="s">
+        <v>41</v>
+      </c>
+      <c r="S1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2">
+        <f>SUM(C2:S2)</f>
+        <v>17</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>1</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>1</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="O2">
+        <v>1</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
+        <f t="shared" ref="B3:B9" si="0">SUM(C3:S3)</f>
+        <v>17</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>1</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+      <c r="F4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>1</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>1</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>1</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <f t="shared" si="0"/>
+        <v>17</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>1</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+      <c r="I8">
+        <v>1</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="K8">
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8">
+        <v>1</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>1</v>
+      </c>
+      <c r="P8">
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>48</v>
+      </c>
+      <c r="B9">
+        <f t="shared" si="0"/>
+        <v>4</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <v>0</v>
+      </c>
+      <c r="L9">
+        <v>0</v>
+      </c>
+      <c r="M9">
+        <v>0</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <v>0</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
+      </c>
+      <c r="S9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>
@@ -2783,7 +9980,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43D914D4-403F-4B81-B472-8E3F05ADF641}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5D405A22-72AA-4B8B-8276-187361E5AFF5}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData/>

--- a/Driver_Experience.xlsx
+++ b/Driver_Experience.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SimonOM\Repositories\Formula-1-Constructor-Repository\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F803CDEC-0708-4AB6-9F8F-4DF322B09974}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7D4150C-E607-49F3-9A66-FDDDAD5E263E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" activeTab="4" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
+    <workbookView xWindow="28680" yWindow="-12660" windowWidth="16440" windowHeight="28320" activeTab="5" xr2:uid="{3A639250-557D-4B08-A9B4-7BAD64B6336B}"/>
   </bookViews>
   <sheets>
     <sheet name="Driver_Lineup_Experience" sheetId="1" r:id="rId1"/>
@@ -1017,10 +1017,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1605,8 +1604,8 @@
   <dimension ref="A1:AL126"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:38" x14ac:dyDescent="0.25">
@@ -1729,30 +1728,9 @@
       <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="2"/>
-      <c r="R2" s="2"/>
-      <c r="S2" s="2"/>
-      <c r="T2" s="2"/>
-      <c r="U2" s="2"/>
-      <c r="V2" s="2"/>
-      <c r="W2" s="2"/>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="2"/>
-      <c r="Z2" s="2"/>
+      <c r="AI2">
+        <v>12</v>
+      </c>
       <c r="AJ2">
         <v>16</v>
       </c>
@@ -1767,30 +1745,9 @@
       <c r="A3" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
-      <c r="O3" s="2"/>
-      <c r="P3" s="2"/>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2"/>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2"/>
-      <c r="V3" s="2"/>
-      <c r="W3" s="2"/>
-      <c r="X3" s="2"/>
-      <c r="Y3" s="2"/>
-      <c r="Z3" s="2"/>
+      <c r="AI3">
+        <v>15</v>
+      </c>
       <c r="AJ3">
         <v>14</v>
       </c>
@@ -1801,30 +1758,6 @@
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
-      <c r="O4" s="2"/>
-      <c r="P4" s="2"/>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2"/>
-      <c r="S4" s="2"/>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2"/>
-      <c r="V4" s="2"/>
-      <c r="W4" s="2"/>
-      <c r="X4" s="2"/>
-      <c r="Y4" s="2"/>
-      <c r="Z4" s="2"/>
       <c r="AC4" s="1"/>
       <c r="AD4" s="1"/>
       <c r="AE4" s="1"/>
@@ -1840,30 +1773,9 @@
       <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2"/>
-      <c r="P5" s="2"/>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2"/>
-      <c r="S5" s="2"/>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2"/>
-      <c r="V5" s="2"/>
-      <c r="W5" s="2"/>
-      <c r="X5" s="2"/>
-      <c r="Y5" s="2"/>
-      <c r="Z5" s="2"/>
+      <c r="AI5">
+        <v>8</v>
+      </c>
       <c r="AJ5" s="1"/>
       <c r="AK5" s="1"/>
       <c r="AL5" s="1"/>
@@ -1872,30 +1784,6 @@
       <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2"/>
-      <c r="P6" s="2"/>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2"/>
-      <c r="S6" s="2"/>
-      <c r="T6" s="2"/>
-      <c r="U6" s="2"/>
-      <c r="V6" s="2"/>
-      <c r="W6" s="2"/>
-      <c r="X6" s="2"/>
-      <c r="Y6" s="2"/>
-      <c r="Z6" s="2"/>
       <c r="AC6" s="1"/>
       <c r="AD6" s="1"/>
       <c r="AE6" s="1"/>
@@ -1911,30 +1799,6 @@
       <c r="A7" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
-      <c r="O7" s="2"/>
-      <c r="P7" s="2"/>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2"/>
-      <c r="S7" s="2"/>
-      <c r="T7" s="2"/>
-      <c r="U7" s="2"/>
-      <c r="V7" s="2"/>
-      <c r="W7" s="2"/>
-      <c r="X7" s="2"/>
-      <c r="Y7" s="2"/>
-      <c r="Z7" s="2"/>
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1"/>
@@ -1946,30 +1810,6 @@
       <c r="A8" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
-      <c r="P8" s="2"/>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2"/>
-      <c r="S8" s="2"/>
-      <c r="T8" s="2"/>
-      <c r="U8" s="2"/>
-      <c r="V8" s="2"/>
-      <c r="W8" s="2"/>
-      <c r="X8" s="2"/>
-      <c r="Y8" s="2"/>
-      <c r="Z8" s="2"/>
       <c r="AB8" s="1"/>
       <c r="AC8" s="1"/>
       <c r="AD8" s="1"/>
@@ -1986,30 +1826,6 @@
       <c r="A9" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
-      <c r="P9" s="2"/>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2"/>
-      <c r="S9" s="2"/>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-      <c r="V9" s="2"/>
-      <c r="W9" s="2"/>
-      <c r="X9" s="2"/>
-      <c r="Y9" s="2"/>
-      <c r="Z9" s="2"/>
       <c r="AD9" s="1"/>
       <c r="AE9" s="1"/>
       <c r="AF9" s="1"/>
@@ -2024,30 +1840,7 @@
       <c r="A10" t="s">
         <v>10</v>
       </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
-      <c r="P10" s="2"/>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2"/>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-      <c r="V10" s="2"/>
-      <c r="W10" s="2"/>
-      <c r="X10" s="2"/>
-      <c r="Y10" s="2"/>
-      <c r="Z10" s="2" t="s">
+      <c r="Z10" t="s">
         <v>152</v>
       </c>
       <c r="AH10" s="1"/>
@@ -2060,30 +1853,9 @@
       <c r="A11" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2"/>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-      <c r="V11" s="2"/>
-      <c r="W11" s="2"/>
-      <c r="X11" s="2"/>
-      <c r="Y11" s="2"/>
-      <c r="Z11" s="2"/>
+      <c r="AI11">
+        <v>15</v>
+      </c>
       <c r="AJ11" s="1"/>
       <c r="AK11" s="1"/>
       <c r="AL11" s="1"/>
@@ -2092,30 +1864,6 @@
       <c r="A12" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-      <c r="V12" s="2"/>
-      <c r="W12" s="2"/>
-      <c r="X12" s="2"/>
-      <c r="Y12" s="2"/>
-      <c r="Z12" s="2"/>
       <c r="AD12" s="1"/>
       <c r="AE12" s="1"/>
       <c r="AF12" s="1"/>
@@ -2130,30 +1878,6 @@
       <c r="A13" t="s">
         <v>13</v>
       </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-      <c r="V13" s="2"/>
-      <c r="W13" s="2"/>
-      <c r="X13" s="2"/>
-      <c r="Y13" s="2"/>
-      <c r="Z13" s="2"/>
       <c r="AG13" s="1"/>
       <c r="AH13" s="1"/>
       <c r="AI13" s="1"/>
@@ -2165,30 +1889,6 @@
       <c r="A14" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-      <c r="V14" s="2"/>
-      <c r="W14" s="2"/>
-      <c r="X14" s="2"/>
-      <c r="Y14" s="2"/>
-      <c r="Z14" s="2"/>
       <c r="AB14" s="1"/>
       <c r="AC14" s="1"/>
       <c r="AD14" s="1"/>
@@ -2205,30 +1905,6 @@
       <c r="A15" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="2"/>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="2"/>
-      <c r="Q15" s="2"/>
-      <c r="R15" s="2"/>
-      <c r="S15" s="2"/>
-      <c r="T15" s="2"/>
-      <c r="U15" s="2"/>
-      <c r="V15" s="2"/>
-      <c r="W15" s="2"/>
-      <c r="X15" s="2"/>
-      <c r="Y15" s="2"/>
-      <c r="Z15" s="2"/>
       <c r="AH15" s="1"/>
       <c r="AI15" s="1"/>
       <c r="AJ15" s="1"/>
@@ -2239,30 +1915,6 @@
       <c r="A16" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="2"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="2"/>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2"/>
-      <c r="S16" s="2"/>
-      <c r="T16" s="2"/>
-      <c r="U16" s="2"/>
-      <c r="V16" s="2"/>
-      <c r="W16" s="2"/>
-      <c r="X16" s="2"/>
-      <c r="Y16" s="2"/>
-      <c r="Z16" s="2"/>
       <c r="AE16" s="1"/>
       <c r="AF16" s="1"/>
       <c r="AG16" s="1"/>
@@ -2276,30 +1928,9 @@
       <c r="A17" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="2"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="2"/>
-      <c r="R17" s="2"/>
-      <c r="S17" s="2"/>
-      <c r="T17" s="2"/>
-      <c r="U17" s="2"/>
-      <c r="V17" s="2"/>
-      <c r="W17" s="2"/>
-      <c r="X17" s="2"/>
-      <c r="Y17" s="2"/>
-      <c r="Z17" s="2"/>
+      <c r="AI17">
+        <v>12</v>
+      </c>
       <c r="AJ17">
         <v>2</v>
       </c>
@@ -2310,30 +1941,6 @@
       <c r="A18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
-      <c r="P18" s="2"/>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2"/>
-      <c r="S18" s="2"/>
-      <c r="T18" s="2"/>
-      <c r="U18" s="2"/>
-      <c r="V18" s="2"/>
-      <c r="W18" s="2"/>
-      <c r="X18" s="2"/>
-      <c r="Y18" s="2"/>
-      <c r="Z18" s="2"/>
       <c r="AB18" s="1"/>
       <c r="AC18" s="1"/>
       <c r="AD18" s="1"/>
@@ -2350,30 +1957,6 @@
       <c r="A19" t="s">
         <v>86</v>
       </c>
-      <c r="C19" s="2"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
-      <c r="M19" s="2"/>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2"/>
-      <c r="S19" s="2"/>
-      <c r="T19" s="2"/>
-      <c r="U19" s="2"/>
-      <c r="V19" s="2"/>
-      <c r="W19" s="2"/>
-      <c r="X19" s="2"/>
-      <c r="Y19" s="2"/>
-      <c r="Z19" s="2"/>
       <c r="AB19" s="1"/>
       <c r="AC19" s="1"/>
       <c r="AD19" s="1"/>
@@ -2390,30 +1973,6 @@
       <c r="A20" t="s">
         <v>19</v>
       </c>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
-      <c r="M20" s="2"/>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="2"/>
-      <c r="Q20" s="2"/>
-      <c r="R20" s="2"/>
-      <c r="S20" s="2"/>
-      <c r="T20" s="2"/>
-      <c r="U20" s="2"/>
-      <c r="V20" s="2"/>
-      <c r="W20" s="2"/>
-      <c r="X20" s="2"/>
-      <c r="Y20" s="2"/>
-      <c r="Z20" s="2"/>
       <c r="AC20" s="1"/>
       <c r="AD20" s="1"/>
       <c r="AE20" s="1"/>
@@ -2429,30 +1988,6 @@
       <c r="A21" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="2"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
-      <c r="M21" s="2"/>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="2"/>
-      <c r="S21" s="2"/>
-      <c r="T21" s="2"/>
-      <c r="U21" s="2"/>
-      <c r="V21" s="2"/>
-      <c r="W21" s="2"/>
-      <c r="X21" s="2"/>
-      <c r="Y21" s="2"/>
-      <c r="Z21" s="2"/>
       <c r="AC21" s="1"/>
       <c r="AD21" s="1"/>
       <c r="AE21" s="1"/>
@@ -2468,30 +2003,9 @@
       <c r="A22" t="s">
         <v>56</v>
       </c>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
-      <c r="M22" s="2"/>
-      <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
-      <c r="P22" s="2"/>
-      <c r="Q22" s="2"/>
-      <c r="R22" s="2"/>
-      <c r="S22" s="2"/>
-      <c r="T22" s="2"/>
-      <c r="U22" s="2"/>
-      <c r="V22" s="2"/>
-      <c r="W22" s="2"/>
-      <c r="X22" s="2"/>
-      <c r="Y22" s="2"/>
-      <c r="Z22" s="2"/>
+      <c r="AI22">
+        <v>15</v>
+      </c>
       <c r="AJ22" s="1"/>
       <c r="AK22" s="1"/>
       <c r="AL22" s="1"/>
@@ -2500,30 +2014,9 @@
       <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="C23" s="2"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="2"/>
-      <c r="M23" s="2"/>
-      <c r="N23" s="2"/>
-      <c r="O23" s="2"/>
-      <c r="P23" s="2"/>
-      <c r="Q23" s="2"/>
-      <c r="R23" s="2"/>
-      <c r="S23" s="2"/>
-      <c r="T23" s="2"/>
-      <c r="U23" s="2"/>
-      <c r="V23" s="2"/>
-      <c r="W23" s="2"/>
-      <c r="X23" s="2"/>
-      <c r="Y23" s="2"/>
-      <c r="Z23" s="2"/>
+      <c r="AI23">
+        <v>2</v>
+      </c>
       <c r="AJ23" s="1"/>
       <c r="AK23" s="1"/>
       <c r="AL23" s="1"/>
@@ -2532,30 +2025,6 @@
       <c r="A24" t="s">
         <v>23</v>
       </c>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="2"/>
-      <c r="M24" s="2"/>
-      <c r="N24" s="2"/>
-      <c r="O24" s="2"/>
-      <c r="P24" s="2"/>
-      <c r="Q24" s="2"/>
-      <c r="R24" s="2"/>
-      <c r="S24" s="2"/>
-      <c r="T24" s="2"/>
-      <c r="U24" s="2"/>
-      <c r="V24" s="2"/>
-      <c r="W24" s="2"/>
-      <c r="X24" s="2"/>
-      <c r="Y24" s="2"/>
-      <c r="Z24" s="2"/>
       <c r="AB24" s="1"/>
       <c r="AC24" s="1"/>
       <c r="AD24" s="1"/>
@@ -2587,30 +2056,6 @@
       <c r="A26" t="s">
         <v>46</v>
       </c>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-      <c r="E26" s="2"/>
-      <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
-      <c r="K26" s="2"/>
-      <c r="L26" s="2"/>
-      <c r="M26" s="2"/>
-      <c r="N26" s="2"/>
-      <c r="O26" s="2"/>
-      <c r="P26" s="2"/>
-      <c r="Q26" s="2"/>
-      <c r="R26" s="2"/>
-      <c r="S26" s="2"/>
-      <c r="T26" s="2"/>
-      <c r="U26" s="2"/>
-      <c r="V26" s="2"/>
-      <c r="W26" s="2"/>
-      <c r="X26" s="2"/>
-      <c r="Y26" s="2"/>
-      <c r="Z26" s="2"/>
       <c r="AA26" s="1"/>
       <c r="AB26" s="1"/>
       <c r="AC26" s="1"/>
@@ -2644,6 +2089,9 @@
     <row r="28" spans="1:38" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>48</v>
+      </c>
+      <c r="AI28">
+        <v>10</v>
       </c>
       <c r="AJ28" s="1"/>
       <c r="AK28" s="1"/>
@@ -9257,8 +8705,10 @@
   <dimension ref="A1:R9"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="23" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="12" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:18" x14ac:dyDescent="0.25">
@@ -9323,9 +8773,54 @@
       </c>
       <c r="B2">
         <f>SUM(C2:R2)</f>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>1</v>
+      </c>
+      <c r="I2">
+        <v>1</v>
+      </c>
+      <c r="J2">
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <v>1</v>
+      </c>
+      <c r="L2">
+        <v>1</v>
+      </c>
+      <c r="M2">
+        <v>0</v>
+      </c>
+      <c r="N2">
+        <v>0</v>
+      </c>
+      <c r="O2">
+        <v>0</v>
+      </c>
+      <c r="P2">
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <v>1</v>
+      </c>
+      <c r="R2">
         <v>1</v>
       </c>
     </row>
@@ -9335,9 +8830,54 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B9" si="0">SUM(C3:R3)</f>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="D3">
+        <v>1</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <v>1</v>
+      </c>
+      <c r="L3">
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <v>1</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="O3">
+        <v>1</v>
+      </c>
+      <c r="P3">
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <v>1</v>
+      </c>
+      <c r="R3">
         <v>1</v>
       </c>
     </row>
@@ -9347,9 +8887,54 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="C4">
+        <v>0</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>1</v>
+      </c>
+      <c r="I4">
+        <v>0</v>
+      </c>
+      <c r="J4">
+        <v>1</v>
+      </c>
+      <c r="K4">
+        <v>1</v>
+      </c>
+      <c r="L4">
+        <v>1</v>
+      </c>
+      <c r="M4">
+        <v>1</v>
+      </c>
+      <c r="N4">
+        <v>1</v>
+      </c>
+      <c r="O4">
+        <v>1</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
         <v>0</v>
       </c>
     </row>
@@ -9359,9 +8944,54 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+      <c r="I5">
+        <v>1</v>
+      </c>
+      <c r="J5">
+        <v>1</v>
+      </c>
+      <c r="K5">
+        <v>1</v>
+      </c>
+      <c r="L5">
+        <v>1</v>
+      </c>
+      <c r="M5">
+        <v>1</v>
+      </c>
+      <c r="N5">
+        <v>1</v>
+      </c>
+      <c r="O5">
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <v>1</v>
+      </c>
+      <c r="R5">
         <v>1</v>
       </c>
     </row>
@@ -9371,9 +9001,54 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C6">
+        <v>1</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+      <c r="I6">
+        <v>1</v>
+      </c>
+      <c r="J6">
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <v>1</v>
+      </c>
+      <c r="N6">
+        <v>1</v>
+      </c>
+      <c r="O6">
+        <v>1</v>
+      </c>
+      <c r="P6">
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <v>1</v>
+      </c>
+      <c r="R6">
         <v>1</v>
       </c>
     </row>
@@ -9383,9 +9058,54 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C7">
+        <v>1</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>1</v>
+      </c>
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+      <c r="I7">
+        <v>1</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <v>1</v>
+      </c>
+      <c r="M7">
+        <v>1</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="O7">
+        <v>1</v>
+      </c>
+      <c r="P7">
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <v>1</v>
+      </c>
+      <c r="R7">
         <v>1</v>
       </c>
     </row>
@@ -9395,10 +9115,55 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C8">
         <v>0</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0</v>
+      </c>
+      <c r="G8">
+        <v>0</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>0</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="K8">
+        <v>0</v>
+      </c>
+      <c r="L8">
+        <v>0</v>
+      </c>
+      <c r="M8">
+        <v>0</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>0</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -9407,10 +9172,55 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C9">
         <v>1</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
+      </c>
+      <c r="K9">
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="O9">
+        <v>1</v>
+      </c>
+      <c r="P9">
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -9491,58 +9301,7 @@
       </c>
       <c r="B2">
         <f>SUM(C2:S2)</f>
-        <v>17</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>1</v>
-      </c>
-      <c r="J2">
-        <v>1</v>
-      </c>
-      <c r="K2">
-        <v>1</v>
-      </c>
-      <c r="L2">
-        <v>1</v>
-      </c>
-      <c r="M2">
-        <v>1</v>
-      </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
-        <v>1</v>
-      </c>
-      <c r="Q2">
-        <v>1</v>
-      </c>
-      <c r="R2">
-        <v>1</v>
-      </c>
-      <c r="S2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -9551,58 +9310,7 @@
       </c>
       <c r="B3">
         <f t="shared" ref="B3:B9" si="0">SUM(C3:S3)</f>
-        <v>17</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-      <c r="D3">
-        <v>1</v>
-      </c>
-      <c r="E3">
-        <v>1</v>
-      </c>
-      <c r="F3">
-        <v>1</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>1</v>
-      </c>
-      <c r="J3">
-        <v>1</v>
-      </c>
-      <c r="K3">
-        <v>1</v>
-      </c>
-      <c r="L3">
-        <v>1</v>
-      </c>
-      <c r="M3">
-        <v>1</v>
-      </c>
-      <c r="N3">
-        <v>1</v>
-      </c>
-      <c r="O3">
-        <v>1</v>
-      </c>
-      <c r="P3">
-        <v>1</v>
-      </c>
-      <c r="Q3">
-        <v>1</v>
-      </c>
-      <c r="R3">
-        <v>1</v>
-      </c>
-      <c r="S3">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:19" x14ac:dyDescent="0.25">
@@ -9611,58 +9319,7 @@
       </c>
       <c r="B4">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C4">
-        <v>1</v>
-      </c>
-      <c r="D4">
-        <v>1</v>
-      </c>
-      <c r="E4">
-        <v>1</v>
-      </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>1</v>
-      </c>
-      <c r="I4">
-        <v>1</v>
-      </c>
-      <c r="J4">
-        <v>1</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-      <c r="L4">
-        <v>1</v>
-      </c>
-      <c r="M4">
-        <v>1</v>
-      </c>
-      <c r="N4">
-        <v>1</v>
-      </c>
-      <c r="O4">
-        <v>1</v>
-      </c>
-      <c r="P4">
-        <v>1</v>
-      </c>
-      <c r="Q4">
-        <v>1</v>
-      </c>
-      <c r="R4">
-        <v>1</v>
-      </c>
-      <c r="S4">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:19" x14ac:dyDescent="0.25">
@@ -9671,58 +9328,7 @@
       </c>
       <c r="B5">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>1</v>
-      </c>
-      <c r="I5">
-        <v>1</v>
-      </c>
-      <c r="J5">
-        <v>1</v>
-      </c>
-      <c r="K5">
-        <v>1</v>
-      </c>
-      <c r="L5">
-        <v>1</v>
-      </c>
-      <c r="M5">
-        <v>1</v>
-      </c>
-      <c r="N5">
-        <v>1</v>
-      </c>
-      <c r="O5">
-        <v>1</v>
-      </c>
-      <c r="P5">
-        <v>1</v>
-      </c>
-      <c r="Q5">
-        <v>1</v>
-      </c>
-      <c r="R5">
-        <v>1</v>
-      </c>
-      <c r="S5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:19" x14ac:dyDescent="0.25">
@@ -9731,58 +9337,7 @@
       </c>
       <c r="B6">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6">
-        <v>1</v>
-      </c>
-      <c r="I6">
-        <v>1</v>
-      </c>
-      <c r="J6">
-        <v>1</v>
-      </c>
-      <c r="K6">
-        <v>1</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6">
-        <v>1</v>
-      </c>
-      <c r="N6">
-        <v>1</v>
-      </c>
-      <c r="O6">
-        <v>1</v>
-      </c>
-      <c r="P6">
-        <v>1</v>
-      </c>
-      <c r="Q6">
-        <v>1</v>
-      </c>
-      <c r="R6">
-        <v>1</v>
-      </c>
-      <c r="S6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:19" x14ac:dyDescent="0.25">
@@ -9791,58 +9346,7 @@
       </c>
       <c r="B7">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C7">
-        <v>1</v>
-      </c>
-      <c r="D7">
-        <v>1</v>
-      </c>
-      <c r="E7">
-        <v>1</v>
-      </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7">
-        <v>1</v>
-      </c>
-      <c r="I7">
-        <v>1</v>
-      </c>
-      <c r="J7">
-        <v>1</v>
-      </c>
-      <c r="K7">
-        <v>1</v>
-      </c>
-      <c r="L7">
-        <v>1</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>1</v>
-      </c>
-      <c r="O7">
-        <v>1</v>
-      </c>
-      <c r="P7">
-        <v>1</v>
-      </c>
-      <c r="Q7">
-        <v>1</v>
-      </c>
-      <c r="R7">
-        <v>1</v>
-      </c>
-      <c r="S7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:19" x14ac:dyDescent="0.25">
@@ -9851,58 +9355,7 @@
       </c>
       <c r="B8">
         <f t="shared" si="0"/>
-        <v>17</v>
-      </c>
-      <c r="C8">
-        <v>1</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-      <c r="E8">
-        <v>1</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8">
-        <v>1</v>
-      </c>
-      <c r="I8">
-        <v>1</v>
-      </c>
-      <c r="J8">
-        <v>1</v>
-      </c>
-      <c r="K8">
-        <v>1</v>
-      </c>
-      <c r="L8">
-        <v>1</v>
-      </c>
-      <c r="M8">
-        <v>1</v>
-      </c>
-      <c r="N8">
-        <v>1</v>
-      </c>
-      <c r="O8">
-        <v>1</v>
-      </c>
-      <c r="P8">
-        <v>1</v>
-      </c>
-      <c r="Q8">
-        <v>1</v>
-      </c>
-      <c r="R8">
-        <v>1</v>
-      </c>
-      <c r="S8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:19" x14ac:dyDescent="0.25">
@@ -9911,57 +9364,6 @@
       </c>
       <c r="B9">
         <f t="shared" si="0"/>
-        <v>4</v>
-      </c>
-      <c r="C9">
-        <v>1</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>0</v>
-      </c>
-      <c r="H9">
-        <v>0</v>
-      </c>
-      <c r="I9">
-        <v>0</v>
-      </c>
-      <c r="J9">
-        <v>0</v>
-      </c>
-      <c r="K9">
-        <v>0</v>
-      </c>
-      <c r="L9">
-        <v>0</v>
-      </c>
-      <c r="M9">
-        <v>0</v>
-      </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
-      <c r="O9">
-        <v>0</v>
-      </c>
-      <c r="P9">
-        <v>0</v>
-      </c>
-      <c r="Q9">
-        <v>0</v>
-      </c>
-      <c r="R9">
-        <v>0</v>
-      </c>
-      <c r="S9">
         <v>0</v>
       </c>
     </row>
